--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/ashland.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/ashland.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ash" sheetId="1" r:id="rId3"/>
+    <sheet name="ash" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="367">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -265,7 +265,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Oh, that paper?
@@ -275,7 +275,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">That is a "land deed". Mysillia is looking for pioneers and we're giving away land for free to promising adventurers.
@@ -285,7 +285,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">
@@ -785,7 +785,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">It pains me to dampen your enthusiasm as you're eager to settle in your new home, but this is something you will eventually learn anyway.
@@ -796,7 +796,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">This land is certainly yours, and you are free to do with it as </t>
@@ -806,7 +806,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">you please. However, as long as it exists within the territory of Mysilia, every asset on this land, down to the last head of livestock, must be recorded in the tax ledger.
@@ -816,7 +816,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">
@@ -1437,459 +1437,6 @@
   <si>
     <t xml:space="preserve">Understood. If that's what you want, then do as you like. If you ever change your mind, feel free to talk to me again.</t>
   </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">能再次见到你真是太好了。据点的开发还顺利吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你已经熟悉提里斯的生活了吗？偶尔出个远门，去各地拜访也不错哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看来你已经能动了嘛。
-我叫阿什兰德。正要和我的同伴去帕罗米亚办事。看起来你还不熟悉这片土地。如果你愿意听的话，我们可以在重新走上旅途前教授你一些生活的智慧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">土地产权证是什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">开拓的目标是什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">请教我生活的智慧</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我有些事情想问你</t>
-  </si>
-  <si>
-    <t xml:space="preserve">感觉好一些了吗？
-首先，我要把这个交给你。
-（男人扔过来一张羊皮纸）
-嗯…这是土地产权证，听起来很厉害吧。就是不知道在当今时代靠这一张纸还能有多少用处了。
-不要客气了，请收下吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">恭喜你，这片土地是你的了。
-为了庆祝这个新的开始，我再送你一把手斧吧。在你接下来开辟土地的时候它一定会有很大的帮助。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">还有，这是米西利亚提供的支援物资，10块金块。
-金块可以用来雇佣居民，还能交换各种发展家园所必须的道具，是非常方便的资源。菲亚玛准备了一些给新手的备用品，别忘了去买啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我们会在这里逗留一段时间，见证一下这片土地的发展。看到你的开拓者之魂燃烧的这么旺盛，让我也产生了一些责任感呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">告示板上贴了一些委托。有空的话就去看看吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊，你问这张纸吗？
-这叫做「土地产权证」。米西利亚正在积极招募开拓者，会把土地免费送给那些未来可期的冒险者们。
-…不过提供的只有土地，不包括供人居住的房屋。所以你必须自己开拓这片土地。自己的地方自己负责，也得当心有魔物或暴徒来袭击你的地盘。另外呢，拥有土地后还要肩负纳税的义务。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没什么好隐瞒的，其实我和菲亚玛都在为米西利亚做事。现在的米西利亚很需要盟友和财源。
-也就是说，我是想让你看在这次救命之恩的份上，指望你建起一个财源滚滚的繁华城镇。
-（男子咧嘴一笑）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这片荒地就是个不错的开拓点。你就找个地方阅读一下产权证吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你想在这片土地建造什么呢？
-不管是为旅人提供歇息的歇脚处，还是名匠挥舞铁锤的工坊，又或是遍布麦田的农村…只要你愿意，都可以成为你的「目标」。
-只要你能缴纳一部分收入作为税收，我们就不会有任何怨言。如果你不知道从哪着手的话，就去告示板看看吧。我张贴了一些可以用作参考的委托。
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你想问什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那位艾莱亚少女是谁？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奈菲亚是什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关于米西利亚的现状</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关于边境公爵赛特拉斯</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关于人类和艾莱亚</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关于托瑞斯家族</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(返回)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你想知道些什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">怎么拾起和使用道具</t>
-  </si>
-  <si>
-    <t xml:space="preserve">采集和疲劳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">制造</t>
-  </si>
-  <si>
-    <t xml:space="preserve">战斗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能力和魔法</t>
-  </si>
-  <si>
-    <t xml:space="preserve">饮食、睡眠、生活</t>
-  </si>
-  <si>
-    <t xml:space="preserve">视野和光源</t>
-  </si>
-  <si>
-    <t xml:space="preserve">首先教你如何拾取和使用道具吧。
-道具会有掉落在地面，和被安装在地面的两种状态。只要走到掉落在地面的道具上就可以将其自动捡起，而被安装好的家具之类的道具则需要用右键点击才能拿起来。
-手中拿着道具时，点击自己可以将道具收纳到背包中，右键点击地面则可以将手里的道具重新安装在指定位置。
-想拾起安装在城镇中的道具则需要偷窃的技术，不过现在还没有学习的必要吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">点击屏幕右下方背包的标志就可以查看背包内容。可以用鼠标拖动的方式来自由移动背包内的道具。
-食物和书之类的道具可以通过右键点击直接使用。另外，用鼠标中键点击道具（或按下R键），可以显示对该道具能作的所有动作哦。
-你可以用鼠标滚轮快速切换屏幕下方的道具栏，把常用工具和消耗品放在快捷栏就可以更方便的使用。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">目前自然资源就可以满足你的生活所需。野蘑菇和莓子都是宝贵的食物来源。等你熟练怎么砍伐树木和加工石材后就可以着手准备制作家具和建筑物的材料了。
-你可以试着用右键采集地图上的资源，但有些道具需要斧头或稿子来进行采集。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">采集等特定行为会消耗你的精力。精力过低时会进入疲劳状态，疲劳时生命值不再自然恢复。如果还要继续工作让精力进一步降低还会有失去意识的风险。
-恢复疲劳的方法比较有限，还请注意控制自己的精力状态。
-当你疲劳到举步难行的时候，在床上睡一觉就能恢复精力了。如果找不到床的话，就试试「休息」能力吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">使用篝火或制作台等设备，可以消耗身上的材料制造道具。
-一开始能造的东西很少，你可以通过开宝箱等方式得到新的配方，阅读之后就可以学会更多道具的制造方法。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">制造的时候除了背包中的素材，还可以使用储存在远处容器内的素材作为材料哦。不过你不可以使用安装在地上的素材和不属于你的素材。
-另外，如果制造道具所需的技能等级不足，就会极大增加精力的消耗。在制造高等级配方之前，先制造一些简单的道具锻炼手艺吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未完</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能力
-能力和魔法有使用次数的限制。
-（未完）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">饮食
-空腹或困倦的时候会停止自愈（未完）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你说在森林中看到了艾莱亚的少女？
-当时你意识不太清楚，我想你看到的大概是和我们同行的伙伴菲亚玛吧。她还在这周围闲逛呢，就是她发现了你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不过菲亚玛是人类，有很多人和你一样都搞错了。
-她…可以听到森林的声音。说到这个，刚才她也说了件奇怪的事…说是梦中的一名少女将把我们引至了此处。那究竟是什么意思啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">提里斯各地都散布着很多无人踏足的遗迹，我们将其称为「奈菲亚的遗迹」，据说奈菲亚的深处沉睡着古代的秘宝。如果你觉得自己本事还不够格，建议还是不要操之过急地去探索比较好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">米西利亚位于北提里斯和南部山脉之间，是由老乔南公爵治理的领地。从很久以前起人类和艾莱亚就一同居住在这里。
-我们的主公赛特拉斯大人和芙琳大人在百年前作为异形之森的使者来到了此处，后来赛特拉斯大人就留在了人类世界之中成为两族共存的象征，也一直都受到领民的崇拜。
-米西利亚虽然说不上富饶，却是个充满希望的和平国度。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">然而，15年前的大战让米西利亚中的不同种族间的关系出现了裂痕。
-面对我们的求助，森之民们选择了沉默，他们对被帝国侵略的提里斯视而不见，这让人类对他们产生了强烈的不信任感。到后来象征着两种族和谐共存的米西利亚中再也不见当年的景象，只剩下两族之间的记恨与对立。
-赛特拉斯大人的声音已经无法传达到人民的耳边。米西利亚的的国民同胞之间开始争夺在荒芜土地上残存的麦穗。而邻国和议会的秃鹫们却都只在幸灾乐祸地观望着这一切。
-这就是这个国家的现状。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">也许米西利亚已经不再有希望，人类和艾莱亚携手前进的日子也不会再回来了。
-但，赛特拉斯大人还没有放弃。我也要为生养我的米西利亚…不，是为了赛特拉斯大人尽力到最后。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在提里斯边境的柳木堡有一位领主，他身为艾莱亚人成为君主，是尼米尔奇迹的英雄。我想你应该也听说过“边境公爵赛特拉斯”的名号吧？
-赛特拉斯大人虽然是异形之森…古老森林的居民，却选择了和芙琳大人共同留在米西利亚，支持着托瑞斯家族的每一代人和米西利亚。他充满智慧，受人崇敬。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">他在十年战争中的功绩依然让人记忆犹新。那天…那一天的光景仍然烙印在所有米西利亚领民的眼中。
-自从与芙琳大人分别之后，赛特拉斯大人就一直躺在床上，表现的沉默寡言。那天晚上，我在柳木堡的城墙上无可奈何地诅咒着在不断逼近米西利亚的萨伊拉飞艇。城堡中的大伙聚集起来商讨对策，这时…赛特拉斯大人竟离开了他自己的房间。他用艾莱亚的语言，悲伤地向天空述说了一句什么话语。
-接着我们就看到一道蓝光闪过尼米尔的天空。然后…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我很难描述当时发生的事情。闪着蓝色光芒的狂风，将萨伊拉飞艇瞬间卷毁。风暴离去之后，在场的人们都哑然无声，大伙都愣神的看着燃烧的飞艇慢慢坠落时发出的红光。赛特拉斯大人的脸上，留下了一道泪水。
-…失去了无敌的萨伊拉飞艇后，帝国开始从提里斯和各地撤退。这就是十年战争终结的经过。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">艾莱亚远在人类文明诞生之前就存在了。在上古世代，人类畏惧着拥有卓越知识和神秘力量的艾莱亚，将他们作为神崇拜，称艾莱亚为母亲。
-艾莱亚是美丽、和平且安详的种族。尽管他们教授了人类很多知识，但却从不会主动积极和人类有什么来往。他们住在蓝色的森林中，很少在人前现身。他们森林的树木会放出瘴气，拒绝着人类的入侵…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">就像你知道的那样，两个种族的关系并不好。人类对旁观十年战争的艾莱亚感到不满。也有人认为艾莱亚的存在妨碍了人类的独立和创造。
-但是，他们什么时候说过自己是人类的同盟者，或保护者呢？是人类擅自将他们称为母亲，又因为被他们忽视而感到愤怒。现在人类所做的事，不就是想通过大声呼喊不公好让自己对艾莱亚的依赖和迁怒正当化吗。
-然而大众并不知道，在推动憎恨声浪的背后一向都隐藏着某些为权力者的目的。呵呵，这里就该说欢迎来到人类的世界了吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赛特拉斯大人和芙琳大人，对于托瑞斯家族来说非常特别。对于我们来说，他们是看着我们长大的亲人，也是会在我们生命的尽头照料我们的司祭。是了解米西利亚和托瑞斯历史的教师，也是分享快乐和悲伤的朋友。
-乔南公爵…我的父亲，即使到了现在，他还是会在赛特拉斯大人面前笑得像个孩子。那是我和弟弟绝对无法看到的一面。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在宽敞而冰冷的米西利亚石造宫廷中，就算是血缘维系的兄弟，却也会偶尔感觉彼此像是陌生人一样。但赛特拉斯大人和芙琳大人之间不会那样，所以我从小就被他们亲密无间、互相支持的模样深深吸引。
-…你想笑我也无所谓。但，只要有赛特拉斯大人和芙琳大人在的地方，就总是充满了和谐。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在这么大的土地上，无论想干什么都需要人手。
-增加居民的方式有很多。可以饲养野生动物，旅途中也可能会有意想不到的邂逅。另外这个大陆的某处似乎有奴隶商人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不过，最简单的方式就是从告示板上雇佣移居志愿者了呢。
-雇佣居民需要被称为灯火的资源。每天的结束时都会得到一些灯火，如果不着急的话用累积的灯火雇佣居民会是个很稳定的方式。
-那就让我来看看你的本事吧。无论用什么方式都好，找个新居民来吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好像找到新同伴了呢。这一定会对开拓土地有所帮助。
-你还可以邀请居民加入队伍一起冒险哦。不过，这样一来同行的居民就不能完成家园里的工作了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那么，今后的开拓和冒险也需要更多人手。我给你定一个家园发展的目标吧。
-目标是，「招募十个居民」。
-也许会花不少时间，完成后记得向我报告。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这地方热闹了不少啊。看来向米西利亚的主公汇报的日子不远了。
-这个卷轴就是达成目标的报酬。这是可以追溯伊尔瓦大地记忆召唤居民的贵重品。要好好使用啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这件事对鼓足干劲开拓新天地的你来说确实有些残酷…但早晚你会知道的。
-首先这片土地当然是属于你的，随便你怎么使用都没关系。只不过，这片土地在米西利亚的领土内，这片土地的所有资产连每一匹家畜都必须记录在税务登记本上，
-你会定期收到税金账单。如果有人滞纳税金，那等待着他的将会是凄惨的命运。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…不过嘛，那是之后的事情了。现在无需担心，专心开拓吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">终于收到了税金账单啊。
-那么让我在这里说明纳税的方法。支付的方式倒是很简单，没什么好担心的。问题在于，怎么准备这笔钱。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">拿到税金账单之后，就去米西利亚首都吧。首都的市政厅里放着纳税箱，带上足够的钱，把税金账单放进去就可以了。
-办完这件要紧事后心情也会放松不少吧。不如在纳完税后顺便物色一下米西利亚市场的特产怎么样？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不止是税金，你将来也会收到各种名目的账单。放宽心，支付方式都是一样的。不过，还是要留意支付期限。滞纳账单的话不仅会降低你的评价，市政厅的家伙们也不介意使用武力。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊对了，有件重要的事情忘了告诉你。向东南方向沿着路走就能到米西利亚。距离稍微有点远，不要迷路啦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">怎么，初次纳税很紧张吗？
-缴税本身并不是很难啦。上次已经说过，问题是怎么准备那些钱。
-给纳完税的你一个不错的礼物吧。只要安装好「邮箱」就能自动收纳送到家园的信和账单，是个很方便的家具。这样一来你就不会错过重要的信息了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在我跟你说明议会有关的事情之前，要先讲讲无聊的历史。
-与东边纷争不绝的艾索里亚相比，北提里斯一直都是片和平的大陆。就算是有萨伊拉飞艇的帝国，也很少踏足这片远隔艾索里亚海的大陆。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但随着新王国耶鲁和帝国之间的摩擦加剧，两国之间的争斗终于让战火洒向了整个世界。提里斯诸国认为有必要联合起来结束这场战争，于是在提里斯和平与繁荣的旗帜下就成立了提里斯联盟。
-联盟提交的议案会在提里斯议会上审议。虽说是议案，但从国家之间的大事到村落援助的小事都有所涉及。而决定议案通过与否的投票权就在议员们的手中。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你在旅途中也许会遇到议会的议员。和他们混个脸熟，得到议会的支持，对家园发展也是非常重要的。
-找到议员后，就先去搭个话吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">北提里斯很广阔。熟悉这里的生活之后，就去四处探索一下吧。
-在东南方向，有个叫做尼米尔的洞窟。洞窟的浅层应该没有很危险的魔物。其实我也对那洞窟有些兴趣，你可以帮忙调查一下吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在出门探索之前，我要把这卷轴交给你。
-只要阅读「脱离卷轴」就可以离开奈菲亚回到地面。
-阅读「归还卷轴」可以让你传送到去过的奈菲亚的最下层或家园。
-它们都是对冒险大有用处的道具。还请好好使用。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你回来了吗。我正担心菲亚突然不见了呢。虽然她经常自己跑去其他地方…
-嗯，先不说这个。让我听听你的报告吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">巨大的…蛾子…？你库莱姆吸多了吧？
-不好意思，这听起来确实让人难以置信，不过既然两个人都看到了，那应该也不是幻觉呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我们寻找的神秘力量，其实是沉睡在地底的以太结晶吗。如果森之淑女欧涅芙说的是真的，那意味着东南方的利萨纳斯遗迹中也沉睡着一个魔石。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">虽然不该轻易相信欧涅芙这种古老存在的话，但我们确实没有其他的选择了。
-利萨纳斯吗…看来有必要去调查一下呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…我还有一件在意的事情。
-你说你见到的人里有一个脖子上纹有没品位纹身的男人？这个人可能是…不，那种家伙找遍提里斯也不会有第二个。
-他肯定是埃夫隆德·托瑞斯。他是米西利亚公爵乔南·托瑞斯的儿子，也是我不成器的弟弟。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">别表现得这么惊讶啊。我已经和托瑞斯家断绝关系了。现在不过是侍奉赛特拉斯大人的一个间谍而已。
-不过话说回来了，埃夫隆德好歹是米西利亚的继承者，怎么会和帝国的人在一起？
-只给人一种不好的预感啊，不过这是我的私事。你就去继续搜集利萨纳斯的情报吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…救你的时候还以为是白费力气，没想到还真是一场奇妙的邂逅。多亏了你，我也听到不少新情报。
-我们要回到柳木堡向赛特拉斯大人进行报告。相处时间不长，也多谢你的帮忙了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果…你对探索利萨纳斯有兴趣的话，不如也来柳木堡一趟吧？
-当然不是强制的。你可以留在这继续发展你的据点，也可以去游历各地长长见识。如何看待这世界，如何留下自己的足迹，都取决于你自己的决定。
-愿你得到风的加护。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">制造是生活和冒险都不可或缺的技术。
-我算不上是专业的，不过会尽己所能地教你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好，首先就从制作台开始吧。制作台是制造的基础设施，使用制作台就能立刻制造地板或墙壁了。
-你只要使用已经学会的「简易制造」能力就可以直接制造制作台了。你就先去砍伐一下那边的树来准备原木，然后试着用「简易制造」造个制作台出来吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没错没错，接下来只需要把完成的制作台安装到合适的地面上就可以了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">做得还不错。
-你试着用过制作台了吗？虽然一开始能做的东西很少，但只要得到新的配方，就可以造更多道具了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这样一来就做好盖房子的准备了，但在这之前，先准备好夜晚的光源比较好。
-只要有光源，就可以在夜晚看到更远的地方。在周围收集素材，用制作台制造「火把」吧。
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">制造「火把」所需的「细绳」要在制作台用「藤蔓」制造。造好火把之后，别忘了把它装备在光源栏上。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好，这样你就踏出了制造者的第一步。要学的东西还有很多，我给你定一个目标吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">目标是「在这片土地上独立建造一栋房子」。
-听起来很麻烦，但只要四面用墙围住再装个门，就可以称为房子了。我去给你准备一些新房贺礼，你就加油盖房子吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看起来你盖好房子了啊，恭喜，这样一来就不用风餐露宿了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">让我来介绍一下房子的用处吧。
-你建造的房子外观和功能，都可以使用建筑告示板来定制。另外，用墙壁分割房子里的空间就可以划分房间，建筑告示板可以用来定制任意一个房间。
-这些建筑牌和房间牌就是我送你的礼物。虽然不算贵重，还请试着定制你的新房子吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在这世道下，学一两种武器的用法一定会派上用场。
-在野外遭遇的大部分生物只要看到你就会攻过来。在装备不齐全的现在，你最好用鼠标悬停在敌人身上查看一下敌人的强度，从而避开和那些强敌战斗。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">首先要进行的是简单的实战训练。我在告示板后面绑了个路过的朋克。被拘束的敌人无法移动，如果觉得危险你可以随时退到安全的距离恢复体力。
-别客气，来尽情揍这个朋克吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">做得好。
-像朋克这种脑袋不灵活的敌人只会用一些简单的攻击手段，没什么好怕的。相对的，你要格外小心使用远程武器的敌人，还有那些和你直接接触后会使出不妙的特殊能力的敌人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">接下来的训练对手是野猪。还是一样绑在告示板后面了。
-野猪和朋克一样都是简单的对手，但可不要小瞧野生动物的战斗能力。近距离硬碰硬的话也有可能会吃亏。
-对付这样的敌人可以用远程攻击。我会给你一些道具，试着花点工夫打倒它吧。别忘了你可以「投掷」道具。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">了不起。这样一来你就会处理那些只会靠蛮力近战的敌人了。
-像野猪这样的对手还算比较容易对付，但如果被它们围住，或被阻断退路，可能也会栽了跟头。无论何时都不要太过自信，一定要准备好随时脱离战斗的手段。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">为了进一步的锻炼，我给你定个目标吧。
-目标就是「打倒一百个敌人」。
-别担心，现在的北提里斯到处都是危险的魔物和恶人。很容易就能遇到一两百个敌人了。至今为止打倒的敌人数量会记录在日志中，忘记的话就看看吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">做得很棒。看来你已经可以保护自己了。
-要学的东西还有很多，但你该做的是继续增加实战的经验。这些白金币就是给你的报酬。
-把白金币交给城里的技能训练师就可以锻炼已有技能，也可以用来学习新技能哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">为了进一步在这片土地上强化你的据点，必须了解什么是「公用容器」才行。
-公用容器是居民生活和工作不可或缺的设备。我只教一次，要仔细记好！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">木箱和桶之类的容器有「权限」这样的概念。一般来说，你安装的容器只有你可以取用里面的道具，但只要点击容器右侧的「锁」图标，就可以将它变成公用容器。
-公用容器可以供居民和队伍成员使用。肚子饿的人会从容器中找食物，看到好装备后就会拿走。如果有工作需要的素材，也会从容器中自取。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">另外，居民会往公用容器中交付发现的物资和工作的产出物，所以要常常查看公用容器的剩余容量。
-你这次的报酬是这个「木箱」。把它安装在地面上，试着变更为「公用容器」吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">已经安装好公用容器了啊。
-变更容器设定，可以做出优先使用的容器，或只放入特定物品的容器。土地开发后需要整理据点内物资的话，就试试这个方法吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你来得正是时候。
-有件事情没和你说过，按规定米西利亚会往开拓地派遣开拓监察官。监察官这个名字有些严肃，但不需要担心。把他当成帮助拓荒的帮手就好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不过嘛，如果你嫌麻烦想自由生活的话，我也可以代替你和米西利亚交涉让他们不派遣监察官过来。
-选择权在你，打算怎么办？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我需要开拓监察官的帮助</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想自由生活</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是吗。我就知道你会这么想，所以已经为了你的开拓地找了一位优秀的监察官。他是我的熟人，虽然性格有点难搞，但工作上无可挑剔。
-让我来介绍吧，我的朋友，也是米西利亚最好的开拓监察官，罗伊特尔。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…这是怎么回事？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我听你说这里是「以后金币会堆积如山的很有潜力的开拓地」，所以才来看看…难道我听错了？
-这地方连地面都没整平，不就是个破荒地吗！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">阿什兰德，你必须给我解释清楚。我可是很忙的。你叫我来这到处是荒草和岩石的未开发地做什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼，看来旅途的疲惫让你忽视了眼前的宝藏啊，罗伊特尔。黄金矿石并不一定只会躺在地上。
-如你所说，这里确实只是片荒地而已。但你看到我旁边这位冒险者了吗？#he才是我叫你来此的理由。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你说这呆头呆脑的冒险者，是金矿石？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…嗯，没错。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…哼，既然你说到了这份上，那我就试试好了。不看好归不看好，我也确实欠你和菲亚不少人情。
-不过啊，唉，这就只是个什么都没有的荒草地。一般来说搞拓荒之前应该做一定的准备才对吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咳哼…啊…那边那位冒险者。总之就是这么回事，以后就由我来担任你的开拓监察官了。
-那我也重新自我介绍一下吧。我叫罗伊特尔。是米西利亚最高级开拓监察官，也是米西利亚宫廷顾问兼宫廷财务官。最喜欢高级奥尔维纳红酒和高效的开拓计划，讨厌的东西是无能的开拓者。
-只要有我的经验和知识，这片开拓地必然会成功。当然这也取决于你的努力。总而言之，好好干吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">罗伊特尔是个严格又认真的男人。一定会对你的开拓发展有很大帮助。
-如果对家园的运营和提里斯生活有疑问，就找他谈谈吧、</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好吧。如果你是这么想的，那就随心所欲吧。如果改变主意的话，也可以随时告诉我。</t>
-  </si>
 </sst>
 </file>
 
@@ -1909,52 +1456,52 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -1994,7 +1541,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -2003,78 +1550,78 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2088,13 +1635,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -2270,26 +1817,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L373"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2327,23 +1874,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>125</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2351,7 +1898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2359,7 +1906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2367,7 +1914,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2375,16 +1922,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="1" t="n">
         <v>117</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -2393,18 +1940,15 @@
       <c r="K16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L16" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="17" ht="13.8">
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="1" t="n">
         <v>118</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -2413,15 +1957,12 @@
       <c r="K17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L17" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="18" ht="64.15">
+    </row>
+    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="4" t="s">
@@ -2430,15 +1971,12 @@
       <c r="K18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L18" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
         <v>32</v>
       </c>
@@ -2448,7 +1986,7 @@
       <c r="E21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J21" s="1" t="s">
@@ -2457,11 +1995,8 @@
       <c r="K21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L21" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="22" ht="12.8">
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
@@ -2471,7 +2006,7 @@
       <c r="E22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J22" s="1" t="s">
@@ -2480,18 +2015,15 @@
       <c r="K22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L22" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="23" ht="12.8">
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2500,18 +2032,15 @@
       <c r="K23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L23" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="24" ht="12.8">
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J24" s="1" t="s">
@@ -2520,11 +2049,8 @@
       <c r="K24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L24" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="25" ht="12.8">
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E25" s="1" t="s">
         <v>47</v>
       </c>
@@ -2532,22 +2058,22 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" ht="12.8">
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E27" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" ht="12.8">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E30" s="1" t="s">
         <v>51</v>
       </c>
@@ -2555,8 +2081,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" ht="95.5">
-      <c r="I31" s="1">
+    <row r="31" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J31" s="4" t="s">
@@ -2565,11 +2091,8 @@
       <c r="K31" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="L31" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="32" ht="12.8">
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="1" t="s">
         <v>55</v>
       </c>
@@ -2577,7 +2100,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E33" s="1" t="s">
         <v>57</v>
       </c>
@@ -2585,7 +2108,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="1" t="s">
         <v>13</v>
       </c>
@@ -2593,13 +2116,13 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="37" ht="53.7">
-      <c r="I37" s="1">
+    <row r="37" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I37" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J37" s="4" t="s">
@@ -2608,11 +2131,8 @@
       <c r="K37" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="L37" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="38" ht="12.8">
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="1" t="s">
         <v>55</v>
       </c>
@@ -2620,8 +2140,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" ht="95.5">
-      <c r="I39" s="1">
+    <row r="39" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I39" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J39" s="4" t="s">
@@ -2630,11 +2150,8 @@
       <c r="K39" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="L39" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="40" ht="12.8">
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E40" s="1" t="s">
         <v>65</v>
       </c>
@@ -2642,8 +2159,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" ht="12.8">
-      <c r="I41" s="1">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J41" s="1" t="s">
@@ -2652,11 +2169,8 @@
       <c r="K41" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L41" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="42" ht="12.8">
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E42" s="1" t="s">
         <v>65</v>
       </c>
@@ -2664,8 +2178,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" ht="22.35">
-      <c r="I43" s="1">
+    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I43" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J43" s="4" t="s">
@@ -2674,11 +2188,8 @@
       <c r="K43" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L43" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="44" ht="12.8">
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E44" s="1" t="s">
         <v>51</v>
       </c>
@@ -2686,7 +2197,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" ht="12.8">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="1" t="s">
         <v>13</v>
       </c>
@@ -2694,13 +2205,13 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="49" ht="103.7">
-      <c r="I49" s="1">
+    <row r="49" customFormat="false" ht="103.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I49" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J49" s="5" t="s">
@@ -2709,12 +2220,9 @@
       <c r="K49" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="L49" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="50" ht="68.65">
-      <c r="I50" s="1">
+    </row>
+    <row r="50" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I50" s="1" t="n">
         <v>12</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -2723,12 +2231,9 @@
       <c r="K50" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="L50" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="51" ht="12.8">
-      <c r="I51" s="1">
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I51" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J51" s="1" t="s">
@@ -2737,22 +2242,19 @@
       <c r="K51" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L51" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="52" ht="12.8">
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="54" ht="12.8">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="55" ht="116.4">
-      <c r="I55" s="1">
+    <row r="55" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I55" s="1" t="n">
         <v>14</v>
       </c>
       <c r="J55" s="4" t="s">
@@ -2761,20 +2263,17 @@
       <c r="K55" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="L55" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="56" ht="12.8">
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="60" ht="12.8">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I60" s="1">
+      <c r="I60" s="1" t="n">
         <v>15</v>
       </c>
       <c r="J60" s="1" t="s">
@@ -2783,18 +2282,15 @@
       <c r="K60" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L60" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="61" ht="12.8">
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I61" s="1">
+      <c r="I61" s="1" t="n">
         <v>16</v>
       </c>
       <c r="J61" s="1" t="s">
@@ -2803,18 +2299,15 @@
       <c r="K61" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L61" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="62" ht="12.8">
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I62" s="1">
+      <c r="I62" s="1" t="n">
         <v>124</v>
       </c>
       <c r="J62" s="1" t="s">
@@ -2823,11 +2316,8 @@
       <c r="K62" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="L62" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="63" ht="12.8">
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="1" t="s">
         <v>90</v>
       </c>
@@ -2837,7 +2327,7 @@
       <c r="E63" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I63" s="1">
+      <c r="I63" s="1" t="n">
         <v>18</v>
       </c>
       <c r="J63" s="1" t="s">
@@ -2846,11 +2336,8 @@
       <c r="K63" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="L63" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="64" ht="12.8">
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="1" t="s">
         <v>94</v>
       </c>
@@ -2860,7 +2347,7 @@
       <c r="E64" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I64" s="1">
+      <c r="I64" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J64" s="1" t="s">
@@ -2869,11 +2356,8 @@
       <c r="K64" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L64" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="65" ht="12.8">
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="1" t="s">
         <v>97</v>
       </c>
@@ -2883,7 +2367,7 @@
       <c r="E65" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I65" s="1">
+      <c r="I65" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J65" s="1" t="s">
@@ -2892,11 +2376,8 @@
       <c r="K65" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="L65" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="66" ht="12.8">
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="1" t="s">
         <v>100</v>
       </c>
@@ -2906,7 +2387,7 @@
       <c r="E66" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I66" s="1">
+      <c r="I66" s="1" t="n">
         <v>21</v>
       </c>
       <c r="J66" s="1" t="s">
@@ -2915,18 +2396,15 @@
       <c r="K66" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="L66" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="67" ht="12.8">
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I67" s="1">
+      <c r="I67" s="1" t="n">
         <v>22</v>
       </c>
       <c r="J67" s="1" t="s">
@@ -2935,11 +2413,8 @@
       <c r="K67" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L67" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="68" ht="12.8">
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="1" t="s">
         <v>13</v>
       </c>
@@ -2947,13 +2422,13 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" ht="12.8">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="74" ht="12.8">
-      <c r="I74" s="1">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I74" s="1" t="n">
         <v>23</v>
       </c>
       <c r="J74" s="1" t="s">
@@ -2962,18 +2437,15 @@
       <c r="K74" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="L74" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="75" ht="12.8">
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="1" t="s">
         <v>108</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I75" s="1">
+      <c r="I75" s="1" t="n">
         <v>24</v>
       </c>
       <c r="J75" s="1" t="s">
@@ -2982,11 +2454,8 @@
       <c r="K75" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="L75" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="76" ht="12.8">
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="1" t="s">
         <v>111</v>
       </c>
@@ -2996,7 +2465,7 @@
       <c r="E76" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I76" s="1">
+      <c r="I76" s="1" t="n">
         <v>25</v>
       </c>
       <c r="J76" s="1" t="s">
@@ -3005,11 +2474,8 @@
       <c r="K76" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L76" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="77" ht="12.8">
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="1" t="s">
         <v>115</v>
       </c>
@@ -3019,7 +2485,7 @@
       <c r="E77" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I77" s="1">
+      <c r="I77" s="1" t="n">
         <v>26</v>
       </c>
       <c r="J77" s="1" t="s">
@@ -3028,11 +2494,8 @@
       <c r="K77" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L77" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="78" ht="12.8">
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="1" t="s">
         <v>119</v>
       </c>
@@ -3042,7 +2505,7 @@
       <c r="E78" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I78" s="1">
+      <c r="I78" s="1" t="n">
         <v>27</v>
       </c>
       <c r="J78" s="1" t="s">
@@ -3051,11 +2514,8 @@
       <c r="K78" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="L78" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="79" ht="12.8">
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="1" t="s">
         <v>123</v>
       </c>
@@ -3065,7 +2525,7 @@
       <c r="E79" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I79" s="1">
+      <c r="I79" s="1" t="n">
         <v>28</v>
       </c>
       <c r="J79" s="1" t="s">
@@ -3074,11 +2534,8 @@
       <c r="K79" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L79" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="80" ht="12.8">
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="1" t="s">
         <v>127</v>
       </c>
@@ -3088,7 +2545,7 @@
       <c r="E80" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I80" s="1">
+      <c r="I80" s="1" t="n">
         <v>29</v>
       </c>
       <c r="J80" s="1" t="s">
@@ -3097,11 +2554,8 @@
       <c r="K80" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="L80" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="81" ht="12.8">
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="1" t="s">
         <v>131</v>
       </c>
@@ -3111,7 +2565,7 @@
       <c r="E81" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I81" s="1">
+      <c r="I81" s="1" t="n">
         <v>30</v>
       </c>
       <c r="J81" s="1" t="s">
@@ -3120,18 +2574,15 @@
       <c r="K81" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="L81" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="82" ht="12.8">
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I82" s="1">
+      <c r="I82" s="1" t="n">
         <v>31</v>
       </c>
       <c r="J82" s="1" t="s">
@@ -3140,11 +2591,8 @@
       <c r="K82" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L82" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="83" ht="12.8">
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="1" t="s">
         <v>13</v>
       </c>
@@ -3152,8 +2600,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="84" ht="12.8">
-      <c r="I84" s="1">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I84" s="1" t="n">
         <v>32</v>
       </c>
       <c r="J84" s="1" t="s">
@@ -3162,16 +2610,13 @@
       <c r="K84" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="L84" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="85" ht="12.8">
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="86" ht="12.8">
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C86" s="1" t="s">
         <v>135</v>
       </c>
@@ -3182,8 +2627,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="87" ht="126.85">
-      <c r="I87" s="1">
+    <row r="87" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I87" s="1" t="n">
         <v>33</v>
       </c>
       <c r="J87" s="4" t="s">
@@ -3192,12 +2637,9 @@
       <c r="K87" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L87" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="88" ht="116.4">
-      <c r="I88" s="1">
+    </row>
+    <row r="88" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I88" s="1" t="n">
         <v>34</v>
       </c>
       <c r="J88" s="4" t="s">
@@ -3206,11 +2648,8 @@
       <c r="K88" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="L88" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="89" ht="12.8">
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="1" t="s">
         <v>41</v>
       </c>
@@ -3218,12 +2657,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="91" ht="12.8">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="92" ht="12.8">
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C92" s="1" t="s">
         <v>141</v>
       </c>
@@ -3234,8 +2673,8 @@
         <v>142</v>
       </c>
     </row>
-    <row r="93" ht="85.05">
-      <c r="I93" s="1">
+    <row r="93" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I93" s="1" t="n">
         <v>35</v>
       </c>
       <c r="J93" s="4" t="s">
@@ -3244,12 +2683,9 @@
       <c r="K93" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="L93" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="94" ht="95.5">
-      <c r="I94" s="1">
+    </row>
+    <row r="94" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I94" s="1" t="n">
         <v>36</v>
       </c>
       <c r="J94" s="4" t="s">
@@ -3258,11 +2694,8 @@
       <c r="K94" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="L94" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="95" ht="12.8">
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="1" t="s">
         <v>41</v>
       </c>
@@ -3270,12 +2703,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="97" ht="12.8">
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="98" ht="12.8">
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C98" s="1" t="s">
         <v>147</v>
       </c>
@@ -3286,8 +2719,8 @@
         <v>148</v>
       </c>
     </row>
-    <row r="99" ht="64.15">
-      <c r="I99" s="1">
+    <row r="99" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I99" s="1" t="n">
         <v>37</v>
       </c>
       <c r="J99" s="4" t="s">
@@ -3296,12 +2729,9 @@
       <c r="K99" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="L99" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="100" ht="74.6">
-      <c r="I100" s="1">
+    </row>
+    <row r="100" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I100" s="1" t="n">
         <v>38</v>
       </c>
       <c r="J100" s="4" t="s">
@@ -3310,11 +2740,8 @@
       <c r="K100" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="L100" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="101" ht="12.8">
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="1" t="s">
         <v>41</v>
       </c>
@@ -3322,12 +2749,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" ht="12.8">
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="105" ht="12.8">
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C105" s="1" t="s">
         <v>153</v>
       </c>
@@ -3338,8 +2765,8 @@
         <v>154</v>
       </c>
     </row>
-    <row r="106" ht="12.8">
-      <c r="I106" s="1">
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I106" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J106" s="1" t="s">
@@ -3348,11 +2775,8 @@
       <c r="K106" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="L106" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="107" ht="12.8">
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="1" t="s">
         <v>41</v>
       </c>
@@ -3360,12 +2784,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="109" ht="12.8">
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="110" ht="12.8">
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C110" s="1" t="s">
         <v>157</v>
       </c>
@@ -3376,8 +2800,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="111" ht="53.7">
-      <c r="I111" s="1">
+    <row r="111" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I111" s="1" t="n">
         <v>40</v>
       </c>
       <c r="J111" s="4" t="s">
@@ -3386,26 +2810,23 @@
       <c r="K111" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="L111" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="112" ht="12.8">
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E112" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="113" ht="12.8">
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="115" ht="12.8">
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="116" ht="12.8">
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C116" s="1" t="s">
         <v>160</v>
       </c>
@@ -3416,8 +2837,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="117" ht="32.8">
-      <c r="I117" s="1">
+    <row r="117" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I117" s="1" t="n">
         <v>41</v>
       </c>
       <c r="J117" s="4" t="s">
@@ -3426,26 +2847,23 @@
       <c r="K117" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="L117" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="118" ht="12.8">
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E118" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="119" ht="12.8">
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="121" ht="12.8">
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="122" ht="12.8">
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C122" s="1" t="s">
         <v>163</v>
       </c>
@@ -3456,8 +2874,8 @@
         <v>164</v>
       </c>
     </row>
-    <row r="123" ht="12.8">
-      <c r="I123" s="1">
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I123" s="1" t="n">
         <v>42</v>
       </c>
       <c r="J123" s="1" t="s">
@@ -3466,25 +2884,22 @@
       <c r="K123" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="L123" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="124" ht="12.8">
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E124" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="125" ht="12.8">
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="134" ht="43.25">
+    <row r="134" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I134" s="1">
+      <c r="I134" s="1" t="n">
         <v>43</v>
       </c>
       <c r="J134" s="4" t="s">
@@ -3493,12 +2908,9 @@
       <c r="K134" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="L134" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="135" ht="53.7">
-      <c r="I135" s="1">
+    </row>
+    <row r="135" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I135" s="1" t="n">
         <v>44</v>
       </c>
       <c r="J135" s="4" t="s">
@@ -3507,22 +2919,19 @@
       <c r="K135" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="L135" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="136" ht="12.8">
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="138" ht="12.8">
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="139" ht="53.7">
-      <c r="I139" s="1">
+    <row r="139" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I139" s="1" t="n">
         <v>45</v>
       </c>
       <c r="J139" s="4" t="s">
@@ -3531,22 +2940,19 @@
       <c r="K139" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="L139" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="140" ht="12.8">
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="142" ht="12.8">
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="143" ht="116.4">
-      <c r="I143" s="1">
+    <row r="143" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I143" s="1" t="n">
         <v>47</v>
       </c>
       <c r="J143" s="4" t="s">
@@ -3555,12 +2961,9 @@
       <c r="K143" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L143" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="144" ht="158.2">
-      <c r="I144" s="1">
+    </row>
+    <row r="144" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I144" s="1" t="n">
         <v>48</v>
       </c>
       <c r="J144" s="4" t="s">
@@ -3569,12 +2972,9 @@
       <c r="K144" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="L144" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="145" ht="64.15">
-      <c r="I145" s="1">
+    </row>
+    <row r="145" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I145" s="1" t="n">
         <v>49</v>
       </c>
       <c r="J145" s="4" t="s">
@@ -3583,22 +2983,19 @@
       <c r="K145" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="L145" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="146" ht="12.8">
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="148" ht="12.8">
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="149" ht="74.6">
-      <c r="I149" s="1">
+    <row r="149" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I149" s="1" t="n">
         <v>50</v>
       </c>
       <c r="J149" s="4" t="s">
@@ -3607,12 +3004,9 @@
       <c r="K149" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="L149" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="150" ht="137.3">
-      <c r="I150" s="1">
+    </row>
+    <row r="150" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I150" s="1" t="n">
         <v>51</v>
       </c>
       <c r="J150" s="4" t="s">
@@ -3621,12 +3015,9 @@
       <c r="K150" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="L150" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="151" ht="105.95">
-      <c r="I151" s="1">
+    </row>
+    <row r="151" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I151" s="1" t="n">
         <v>52</v>
       </c>
       <c r="J151" s="4" t="s">
@@ -3635,22 +3026,19 @@
       <c r="K151" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="L151" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="152" ht="12.8">
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="156" ht="12.8">
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="157" ht="105.95">
-      <c r="I157" s="1">
+    <row r="157" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I157" s="1" t="n">
         <v>53</v>
       </c>
       <c r="J157" s="4" t="s">
@@ -3659,12 +3047,9 @@
       <c r="K157" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="L157" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="158" ht="147.75">
-      <c r="I158" s="1">
+    </row>
+    <row r="158" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I158" s="1" t="n">
         <v>54</v>
       </c>
       <c r="J158" s="4" t="s">
@@ -3673,22 +3058,19 @@
       <c r="K158" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="L158" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="160" ht="12.8">
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B160" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="162" ht="12.8">
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="163" ht="85.05">
-      <c r="I163" s="1">
+    <row r="163" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I163" s="1" t="n">
         <v>55</v>
       </c>
       <c r="J163" s="4" t="s">
@@ -3697,12 +3079,9 @@
       <c r="K163" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="L163" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="164" ht="64.15">
-      <c r="I164" s="1">
+    </row>
+    <row r="164" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I164" s="1" t="n">
         <v>56</v>
       </c>
       <c r="J164" s="4" t="s">
@@ -3711,21 +3090,18 @@
       <c r="K164" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="L164" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="166" ht="12.8">
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="172" ht="12.8">
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="173" ht="12.8">
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E173" s="1" t="s">
         <v>192</v>
       </c>
@@ -3733,44 +3109,38 @@
         <v>193</v>
       </c>
     </row>
-    <row r="174" ht="12.8">
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E174" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="175" ht="12.8">
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E175" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="181" ht="12.8">
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="183" ht="53.7">
-      <c r="I183" s="1">
+    <row r="183" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I183" s="1" t="n">
         <v>57</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="L183" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="184" ht="85.05">
-      <c r="I184" s="1">
+    </row>
+    <row r="184" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I184" s="1" t="n">
         <v>58</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="L184" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="185" ht="12.8">
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E185" s="1" t="s">
         <v>199</v>
       </c>
@@ -3778,80 +3148,71 @@
         <v>200</v>
       </c>
     </row>
-    <row r="186" ht="12.8">
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E186" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="188" ht="12.8">
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="189" ht="53.7">
-      <c r="I189" s="1">
+    <row r="189" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I189" s="1" t="n">
         <v>59</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="L189" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="190" ht="64.15">
-      <c r="I190" s="1">
+    </row>
+    <row r="190" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I190" s="1" t="n">
         <v>60</v>
       </c>
       <c r="J190" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="L190" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="191" ht="12.8">
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E191" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="192" ht="12.8">
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="193" ht="53.7">
-      <c r="I193" s="1">
+    <row r="193" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I193" s="1" t="n">
         <v>61</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="L193" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="194" ht="12.8">
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E194" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="195" ht="12.8">
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E195" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="197" ht="12.8">
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="199" ht="12.8">
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J199" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="200" ht="12.8">
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E200" s="1" t="s">
         <v>199</v>
       </c>
@@ -3859,33 +3220,33 @@
         <v>208</v>
       </c>
     </row>
-    <row r="201" ht="12.8">
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E201" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="203" ht="12.8">
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="205" ht="12.8">
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J205" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="206" ht="12.8">
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E206" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="208" ht="12.8">
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="209" ht="124.6">
-      <c r="I209" s="1">
+    <row r="209" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I209" s="1" t="n">
         <v>62</v>
       </c>
       <c r="J209" s="4" t="s">
@@ -3894,12 +3255,9 @@
       <c r="K209" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="L209" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="210" ht="12.8">
-      <c r="I210" s="1">
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I210" s="1" t="n">
         <v>63</v>
       </c>
       <c r="J210" s="1" t="s">
@@ -3908,11 +3266,8 @@
       <c r="K210" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="L210" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="211" ht="12.8">
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E211" s="1" t="s">
         <v>199</v>
       </c>
@@ -3920,18 +3275,18 @@
         <v>216</v>
       </c>
     </row>
-    <row r="212" ht="12.8">
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E212" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="214" ht="12.8">
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="216" ht="53.7">
-      <c r="I216" s="1">
+    <row r="216" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I216" s="1" t="n">
         <v>64</v>
       </c>
       <c r="J216" s="4" t="s">
@@ -3940,12 +3295,9 @@
       <c r="K216" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="L216" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="217" ht="74.6">
-      <c r="I217" s="1">
+    </row>
+    <row r="217" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I217" s="1" t="n">
         <v>65</v>
       </c>
       <c r="J217" s="4" t="s">
@@ -3954,12 +3306,9 @@
       <c r="K217" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="L217" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="218" ht="12.8">
-      <c r="I218" s="1">
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I218" s="1" t="n">
         <v>66</v>
       </c>
       <c r="J218" s="1" t="s">
@@ -3968,12 +3317,9 @@
       <c r="K218" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="L218" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="219" ht="12.8">
-      <c r="I219" s="1">
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I219" s="1" t="n">
         <v>67</v>
       </c>
       <c r="J219" s="1" t="s">
@@ -3982,27 +3328,24 @@
       <c r="K219" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L219" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="220" ht="12.8">
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E220" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="221" ht="12.8">
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="222" ht="12.8">
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E222" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="223" ht="105.95">
-      <c r="I223" s="1">
+    <row r="223" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I223" s="1" t="n">
         <v>68</v>
       </c>
       <c r="J223" s="4" t="s">
@@ -4011,22 +3354,19 @@
       <c r="K223" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="L223" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="224" ht="12.8">
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E224" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="225" ht="12.8">
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="227" ht="74.6">
-      <c r="I227" s="1">
+    <row r="227" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I227" s="1" t="n">
         <v>69</v>
       </c>
       <c r="J227" s="4" t="s">
@@ -4035,12 +3375,9 @@
       <c r="K227" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="L227" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="228" ht="116.4">
-      <c r="I228" s="1">
+    </row>
+    <row r="228" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I228" s="1" t="n">
         <v>70</v>
       </c>
       <c r="J228" s="4" t="s">
@@ -4049,12 +3386,9 @@
       <c r="K228" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="L228" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="229" ht="53.7">
-      <c r="I229" s="1">
+    </row>
+    <row r="229" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I229" s="1" t="n">
         <v>71</v>
       </c>
       <c r="J229" s="4" t="s">
@@ -4063,11 +3397,8 @@
       <c r="K229" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="L229" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="230" ht="12.8">
+    </row>
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E230" s="1" t="s">
         <v>199</v>
       </c>
@@ -4075,33 +3406,33 @@
         <v>236</v>
       </c>
     </row>
-    <row r="231" ht="12.8">
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E231" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="233" ht="12.8">
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="235" ht="12.8">
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J235" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="236" ht="12.8">
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E236" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="238" ht="12.8">
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="240" ht="74.6">
-      <c r="I240" s="1">
+    <row r="240" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I240" s="1" t="n">
         <v>72</v>
       </c>
       <c r="J240" s="4" t="s">
@@ -4110,11 +3441,8 @@
       <c r="K240" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="L240" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="241" ht="12.8">
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E241" s="1" t="s">
         <v>65</v>
       </c>
@@ -4122,8 +3450,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="242" ht="85.05">
-      <c r="I242" s="1">
+    <row r="242" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I242" s="1" t="n">
         <v>73</v>
       </c>
       <c r="J242" s="4" t="s">
@@ -4132,11 +3460,8 @@
       <c r="K242" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="L242" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="243" ht="12.8">
+    </row>
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E243" s="1" t="s">
         <v>199</v>
       </c>
@@ -4144,17 +3469,17 @@
         <v>245</v>
       </c>
     </row>
-    <row r="244" ht="12.8">
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E244" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="247" ht="12.8">
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="248" ht="12.8">
+    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E248" s="1" t="s">
         <v>14</v>
       </c>
@@ -4162,8 +3487,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="249" ht="43.25">
-      <c r="I249" s="1">
+    <row r="249" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I249" s="1" t="n">
         <v>74</v>
       </c>
       <c r="J249" s="4" t="s">
@@ -4172,11 +3497,8 @@
       <c r="K249" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="L249" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="250" ht="12.8">
+    </row>
+    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E250" s="1" t="s">
         <v>250</v>
       </c>
@@ -4184,7 +3506,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="251" ht="12.8">
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E251" s="1" t="s">
         <v>252</v>
       </c>
@@ -4192,7 +3514,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="252" ht="12.8">
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E252" s="1" t="s">
         <v>253</v>
       </c>
@@ -4200,7 +3522,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="253" ht="12.8">
+    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E253" s="1" t="s">
         <v>254</v>
       </c>
@@ -4208,8 +3530,8 @@
         <v>255</v>
       </c>
     </row>
-    <row r="254" ht="43.25">
-      <c r="I254" s="1">
+    <row r="254" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I254" s="1" t="n">
         <v>75</v>
       </c>
       <c r="J254" s="4" t="s">
@@ -4218,12 +3540,9 @@
       <c r="K254" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="L254" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="255" ht="12.8">
-      <c r="I255" s="1">
+    </row>
+    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I255" s="1" t="n">
         <v>76</v>
       </c>
       <c r="J255" s="1" t="s">
@@ -4232,12 +3551,9 @@
       <c r="K255" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="L255" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="256" ht="43.25">
-      <c r="I256" s="1">
+    </row>
+    <row r="256" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I256" s="1" t="n">
         <v>77</v>
       </c>
       <c r="J256" s="4" t="s">
@@ -4246,12 +3562,9 @@
       <c r="K256" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="L256" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="257" ht="85.05">
-      <c r="I257" s="1">
+    </row>
+    <row r="257" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I257" s="1" t="n">
         <v>78</v>
       </c>
       <c r="J257" s="4" t="s">
@@ -4260,12 +3573,9 @@
       <c r="K257" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="L257" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="258" ht="85.05">
-      <c r="I258" s="1">
+    </row>
+    <row r="258" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I258" s="1" t="n">
         <v>79</v>
       </c>
       <c r="J258" s="4" t="s">
@@ -4274,12 +3584,9 @@
       <c r="K258" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="L258" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="259" ht="64.15">
-      <c r="I259" s="1">
+    </row>
+    <row r="259" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I259" s="1" t="n">
         <v>80</v>
       </c>
       <c r="J259" s="4" t="s">
@@ -4288,12 +3595,9 @@
       <c r="K259" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="L259" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="261" ht="95.5">
-      <c r="I261" s="1">
+    </row>
+    <row r="261" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I261" s="1" t="n">
         <v>81</v>
       </c>
       <c r="J261" s="4" t="s">
@@ -4302,16 +3606,13 @@
       <c r="K261" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="L261" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="264" ht="12.8">
+    </row>
+    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E264" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="265" ht="12.8">
+    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E265" s="1" t="s">
         <v>65</v>
       </c>
@@ -4319,18 +3620,18 @@
         <v>270</v>
       </c>
     </row>
-    <row r="266" ht="12.8">
+    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E266" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="270" ht="12.8">
+    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="272" ht="32.8">
-      <c r="I272" s="1">
+    <row r="272" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I272" s="1" t="n">
         <v>82</v>
       </c>
       <c r="J272" s="4" t="s">
@@ -4339,12 +3640,9 @@
       <c r="K272" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="L272" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="273" ht="85.05">
-      <c r="I273" s="1">
+    </row>
+    <row r="273" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I273" s="1" t="n">
         <v>83</v>
       </c>
       <c r="J273" s="4" t="s">
@@ -4353,12 +3651,9 @@
       <c r="K273" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="L273" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="274" ht="12.8">
-      <c r="I274" s="1">
+    </row>
+    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I274" s="1" t="n">
         <v>84</v>
       </c>
       <c r="J274" s="1" t="s">
@@ -4367,11 +3662,8 @@
       <c r="K274" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="L274" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="275" ht="12.8">
+    </row>
+    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E275" s="1" t="s">
         <v>199</v>
       </c>
@@ -4379,18 +3671,18 @@
         <v>278</v>
       </c>
     </row>
-    <row r="276" ht="12.8">
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E276" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="278" ht="12.8">
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="280" ht="53.7">
-      <c r="I280" s="1">
+    <row r="280" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I280" s="1" t="n">
         <v>85</v>
       </c>
       <c r="J280" s="4" t="s">
@@ -4399,12 +3691,9 @@
       <c r="K280" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="L280" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="281" ht="64.15">
-      <c r="I281" s="1">
+    </row>
+    <row r="281" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I281" s="1" t="n">
         <v>86</v>
       </c>
       <c r="J281" s="4" t="s">
@@ -4413,12 +3702,9 @@
       <c r="K281" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="L281" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="282" ht="12.8">
-      <c r="I282" s="1">
+    </row>
+    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I282" s="1" t="n">
         <v>102</v>
       </c>
       <c r="J282" s="1" t="s">
@@ -4427,22 +3713,19 @@
       <c r="K282" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L282" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="283" ht="12.8">
+    </row>
+    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E283" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="285" ht="12.8">
+    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="287" ht="12.8">
-      <c r="I287" s="1">
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I287" s="1" t="n">
         <v>87</v>
       </c>
       <c r="J287" s="1" t="s">
@@ -4451,12 +3734,9 @@
       <c r="K287" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="L287" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="288" ht="64.15">
-      <c r="I288" s="1">
+    </row>
+    <row r="288" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I288" s="1" t="n">
         <v>88</v>
       </c>
       <c r="J288" s="4" t="s">
@@ -4465,22 +3745,19 @@
       <c r="K288" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="L288" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="289" ht="12.8">
+    </row>
+    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E289" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="291" ht="12.8">
+    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="292" ht="12.8">
-      <c r="I292" s="1">
+    <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I292" s="1" t="n">
         <v>89</v>
       </c>
       <c r="J292" s="1" t="s">
@@ -4489,12 +3766,9 @@
       <c r="K292" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="L292" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="293" ht="95.5">
-      <c r="I293" s="1">
+    </row>
+    <row r="293" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I293" s="1" t="n">
         <v>90</v>
       </c>
       <c r="J293" s="4" t="s">
@@ -4503,27 +3777,24 @@
       <c r="K293" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="L293" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="294" ht="12.8">
+    </row>
+    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E294" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="295" ht="12.8">
+    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E295" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="298" ht="12.8">
+    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="299" ht="74.6">
-      <c r="I299" s="1">
+    <row r="299" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I299" s="1" t="n">
         <v>91</v>
       </c>
       <c r="J299" s="4" t="s">
@@ -4532,12 +3803,9 @@
       <c r="K299" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="L299" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="300" ht="74.6">
-      <c r="I300" s="1">
+    </row>
+    <row r="300" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I300" s="1" t="n">
         <v>92</v>
       </c>
       <c r="J300" s="4" t="s">
@@ -4546,11 +3814,8 @@
       <c r="K300" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="L300" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="301" ht="12.8">
+    </row>
+    <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E301" s="1" t="s">
         <v>65</v>
       </c>
@@ -4558,7 +3823,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="302" ht="12.8">
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E302" s="1" t="s">
         <v>199</v>
       </c>
@@ -4566,18 +3831,18 @@
         <v>302</v>
       </c>
     </row>
-    <row r="303" ht="12.8">
+    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E303" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="305" ht="12.8">
+    <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="306" ht="64.15">
-      <c r="I306" s="1">
+    <row r="306" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I306" s="1" t="n">
         <v>93</v>
       </c>
       <c r="J306" s="4" t="s">
@@ -4586,12 +3851,9 @@
       <c r="K306" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="L306" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="307" ht="116.4">
-      <c r="I307" s="1">
+    </row>
+    <row r="307" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I307" s="1" t="n">
         <v>94</v>
       </c>
       <c r="J307" s="4" t="s">
@@ -4600,11 +3862,8 @@
       <c r="K307" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="L307" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="308" ht="12.8">
+    </row>
+    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E308" s="1" t="s">
         <v>65</v>
       </c>
@@ -4612,18 +3871,18 @@
         <v>308</v>
       </c>
     </row>
-    <row r="309" ht="12.8">
+    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E309" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="311" ht="12.8">
+    <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="312" ht="85.05">
-      <c r="I312" s="1">
+    <row r="312" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I312" s="1" t="n">
         <v>95</v>
       </c>
       <c r="J312" s="4" t="s">
@@ -4632,12 +3891,9 @@
       <c r="K312" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="L312" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="313" ht="95.5">
-      <c r="I313" s="1">
+    </row>
+    <row r="313" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I313" s="1" t="n">
         <v>96</v>
       </c>
       <c r="J313" s="4" t="s">
@@ -4646,27 +3902,24 @@
       <c r="K313" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="L313" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="314" ht="12.8">
+    </row>
+    <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E314" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="316" ht="12.8">
+    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="317" ht="12.8">
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E317" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="318" ht="74.6">
-      <c r="I318" s="1">
+    <row r="318" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I318" s="1" t="n">
         <v>97</v>
       </c>
       <c r="J318" s="4" t="s">
@@ -4675,22 +3928,19 @@
       <c r="K318" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="L318" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="320" ht="12.8">
+    </row>
+    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E320" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="323" ht="12.8">
+    <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="324" ht="64.15">
-      <c r="I324" s="1">
+    <row r="324" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I324" s="1" t="n">
         <v>98</v>
       </c>
       <c r="J324" s="4" t="s">
@@ -4699,12 +3949,9 @@
       <c r="K324" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="L324" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="325" ht="105.95">
-      <c r="I325" s="1">
+    </row>
+    <row r="325" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I325" s="1" t="n">
         <v>99</v>
       </c>
       <c r="J325" s="4" t="s">
@@ -4713,12 +3960,9 @@
       <c r="K325" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="L325" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="326" ht="74.6">
-      <c r="I326" s="1">
+    </row>
+    <row r="326" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I326" s="1" t="n">
         <v>100</v>
       </c>
       <c r="J326" s="4" t="s">
@@ -4727,11 +3971,8 @@
       <c r="K326" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="L326" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="328" ht="12.8">
+    </row>
+    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E328" s="1" t="s">
         <v>65</v>
       </c>
@@ -4739,7 +3980,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="329" ht="12.8">
+    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E329" s="1" t="s">
         <v>199</v>
       </c>
@@ -4747,23 +3988,23 @@
         <v>325</v>
       </c>
     </row>
-    <row r="330" ht="12.8">
+    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E330" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="332" ht="12.8">
+    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="334" ht="12.8">
+    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E334" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="335" ht="74.6">
-      <c r="I335" s="1">
+    <row r="335" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I335" s="1" t="n">
         <v>101</v>
       </c>
       <c r="J335" s="4" t="s">
@@ -4772,21 +4013,18 @@
       <c r="K335" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="L335" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="336" ht="12.8">
+    </row>
+    <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E336" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="338" ht="12.8">
+    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="339" ht="12.8">
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E339" s="1" t="s">
         <v>14</v>
       </c>
@@ -4794,11 +4032,11 @@
         <v>330</v>
       </c>
     </row>
-    <row r="341" ht="12.8">
+    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F341" s="8"/>
     </row>
-    <row r="342" ht="64.15">
-      <c r="I342" s="1">
+    <row r="342" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I342" s="1" t="n">
         <v>103</v>
       </c>
       <c r="J342" s="5" t="s">
@@ -4807,12 +4045,9 @@
       <c r="K342" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="L342" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="343" ht="46.25">
-      <c r="I343" s="1">
+    </row>
+    <row r="343" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I343" s="1" t="n">
         <v>120</v>
       </c>
       <c r="J343" s="5" t="s">
@@ -4821,18 +4056,15 @@
       <c r="K343" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="L343" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="344" ht="13.8">
+    </row>
+    <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B344" s="1" t="s">
         <v>335</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I344" s="1">
+      <c r="I344" s="1" t="n">
         <v>121</v>
       </c>
       <c r="J344" s="5" t="s">
@@ -4841,18 +4073,15 @@
       <c r="K344" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="L344" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="345" ht="13.8">
+    </row>
+    <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B345" s="1" t="s">
         <v>338</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I345" s="1">
+      <c r="I345" s="1" t="n">
         <v>122</v>
       </c>
       <c r="J345" s="5" t="s">
@@ -4861,22 +4090,19 @@
       <c r="K345" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="L345" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="346" ht="13.8">
+    </row>
+    <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J346" s="5"/>
       <c r="K346" s="4"/>
     </row>
-    <row r="347" ht="13.8">
+    <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
         <v>335</v>
       </c>
       <c r="J347" s="5"/>
       <c r="K347" s="4"/>
     </row>
-    <row r="348" ht="13.8">
+    <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E348" s="1" t="s">
         <v>199</v>
       </c>
@@ -4886,8 +4112,8 @@
       <c r="J348" s="5"/>
       <c r="K348" s="4"/>
     </row>
-    <row r="349" ht="64.15">
-      <c r="I349" s="1">
+    <row r="349" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I349" s="1" t="n">
         <v>125</v>
       </c>
       <c r="J349" s="5" t="s">
@@ -4896,15 +4122,12 @@
       <c r="K349" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="L349" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="350" ht="13.8">
+    </row>
+    <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G350" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I350" s="1">
+      <c r="I350" s="1" t="n">
         <v>108</v>
       </c>
       <c r="J350" s="5" t="s">
@@ -4913,15 +4136,12 @@
       <c r="K350" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="L350" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="351" ht="13.8">
+    </row>
+    <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G351" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I351" s="1">
+      <c r="I351" s="1" t="n">
         <v>109</v>
       </c>
       <c r="J351" s="5" t="s">
@@ -4930,15 +4150,12 @@
       <c r="K351" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="L351" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="352" ht="53.7">
+    </row>
+    <row r="352" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G352" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I352" s="1">
+      <c r="I352" s="1" t="n">
         <v>110</v>
       </c>
       <c r="J352" s="5" t="s">
@@ -4947,15 +4164,12 @@
       <c r="K352" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="L352" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="353" ht="13.8">
+    </row>
+    <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G353" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I353" s="1">
+      <c r="I353" s="1" t="n">
         <v>104</v>
       </c>
       <c r="J353" s="3" t="s">
@@ -4964,12 +4178,9 @@
       <c r="K353" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="L353" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="354" ht="64.15">
-      <c r="I354" s="1">
+    </row>
+    <row r="354" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I354" s="1" t="n">
         <v>105</v>
       </c>
       <c r="J354" s="5" t="s">
@@ -4978,15 +4189,12 @@
       <c r="K354" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="L354" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="355" ht="12.8">
+    </row>
+    <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G355" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I355" s="1">
+      <c r="I355" s="1" t="n">
         <v>111</v>
       </c>
       <c r="J355" s="1" t="s">
@@ -4995,15 +4203,12 @@
       <c r="K355" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="L355" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="356" ht="12.8">
+    </row>
+    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G356" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="I356" s="1">
+      <c r="I356" s="1" t="n">
         <v>119</v>
       </c>
       <c r="J356" s="1" t="s">
@@ -5012,12 +4217,9 @@
       <c r="K356" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="L356" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="357" ht="12.8">
-      <c r="I357" s="1">
+    </row>
+    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I357" s="1" t="n">
         <v>107</v>
       </c>
       <c r="J357" s="1" t="s">
@@ -5026,15 +4228,12 @@
       <c r="K357" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="L357" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="358" ht="13.8">
+    </row>
+    <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G358" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I358" s="1">
+      <c r="I358" s="1" t="n">
         <v>112</v>
       </c>
       <c r="J358" s="3" t="s">
@@ -5043,12 +4242,9 @@
       <c r="K358" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="L358" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="359" ht="13.8">
-      <c r="I359" s="1">
+    </row>
+    <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I359" s="1" t="n">
         <v>113</v>
       </c>
       <c r="J359" s="10" t="s">
@@ -5057,15 +4253,12 @@
       <c r="K359" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="L359" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="360" ht="74.6">
+    </row>
+    <row r="360" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G360" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I360" s="1">
+      <c r="I360" s="1" t="n">
         <v>114</v>
       </c>
       <c r="J360" s="5" t="s">
@@ -5074,15 +4267,12 @@
       <c r="K360" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="L360" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="361" ht="105.95">
+    </row>
+    <row r="361" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G361" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I361" s="1">
+      <c r="I361" s="1" t="n">
         <v>115</v>
       </c>
       <c r="J361" s="5" t="s">
@@ -5091,12 +4281,9 @@
       <c r="K361" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="L361" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="362" ht="61.15">
-      <c r="I362" s="1">
+    </row>
+    <row r="362" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I362" s="1" t="n">
         <v>116</v>
       </c>
       <c r="J362" s="11" t="s">
@@ -5105,27 +4292,24 @@
       <c r="K362" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="L362" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="363" ht="12.8">
+    </row>
+    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E363" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="365" ht="12.8">
+    <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E365" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="369" ht="12.8">
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="371" ht="12.8">
-      <c r="I371" s="1">
+    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I371" s="1" t="n">
         <v>123</v>
       </c>
       <c r="J371" s="1" t="s">
@@ -5134,23 +4318,20 @@
       <c r="K371" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="L371" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="373" ht="12.8">
+    </row>
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E373" s="1" t="s">
         <v>195</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/ashland.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/ashland.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="ash" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="ash" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="483">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -265,7 +265,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Oh, that paper?
@@ -275,7 +275,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">That is a "land deed". Mysillia is looking for pioneers and we're giving away land for free to promising adventurers.
@@ -285,7 +285,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">
@@ -785,7 +785,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">It pains me to dampen your enthusiasm as you're eager to settle in your new home, but this is something you will eventually learn anyway.
@@ -796,7 +796,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">This land is certainly yours, and you are free to do with it as </t>
@@ -806,7 +806,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">you please. However, as long as it exists within the territory of Mysilia, every asset on this land, down to the last head of livestock, must be recorded in the tax ledger.
@@ -816,7 +816,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">
@@ -1437,6 +1437,459 @@
   <si>
     <t xml:space="preserve">Understood. If that's what you want, then do as you like. If you ever change your mind, feel free to talk to me again.</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">能再次见到你真是太好了。据点的开发还顺利吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你已经熟悉提里斯的生活了吗？偶尔出个远门，去各地拜访也不错哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看来你已经能动了嘛。
+我叫阿什兰德。正要和我的同伴去帕罗米亚办事。看起来你还不熟悉这片土地。如果你愿意听的话，我们可以在重新走上旅途前教授你一些生活的智慧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">土地产权证是什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">开拓的目标是什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请教我生活的智慧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我有些事情想问你</t>
+  </si>
+  <si>
+    <t xml:space="preserve">感觉好一些了吗？
+首先，我要把这个交给你。
+（男人扔过来一张羊皮纸）
+嗯…这是土地产权证，听起来很厉害吧。就是不知道在当今时代靠这一张纸还能有多少用处了。
+不要客气了，请收下吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恭喜你，这片土地是你的了。
+为了庆祝这个新的开始，我再送你一把手斧吧。在你接下来开辟土地的时候它一定会有很大的帮助。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">还有，这是米西利亚提供的支援物资，10块金块。
+金块可以用来雇佣居民，还能交换各种发展家园所必须的道具，是非常方便的资源。菲亚玛准备了一些给新手的备用品，别忘了去买啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我们会在这里逗留一段时间，见证一下这片土地的发展。看到你的开拓者之魂燃烧的这么旺盛，让我也产生了一些责任感呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">告示板上贴了一些委托。有空的话就去看看吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊，你问这张纸吗？
+这叫做「土地产权证」。米西利亚正在积极招募开拓者，会把土地免费送给那些未来可期的冒险者们。
+…不过提供的只有土地，不包括供人居住的房屋。所以你必须自己开拓这片土地。自己的地方自己负责，也得当心有魔物或暴徒来袭击你的地盘。另外呢，拥有土地后还要肩负纳税的义务。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没什么好隐瞒的，其实我和菲亚玛都在为米西利亚做事。现在的米西利亚很需要盟友和财源。
+也就是说，我是想让你看在这次救命之恩的份上，指望你建起一个财源滚滚的繁华城镇。
+（男子咧嘴一笑）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这片荒地就是个不错的开拓点。你就找个地方阅读一下产权证吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你想在这片土地建造什么呢？
+不管是为旅人提供歇息的歇脚处，还是名匠挥舞铁锤的工坊，又或是遍布麦田的农村…只要你愿意，都可以成为你的「目标」。
+只要你能缴纳一部分收入作为税收，我们就不会有任何怨言。如果你不知道从哪着手的话，就去告示板看看吧。我张贴了一些可以用作参考的委托。
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你想问什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那位艾莱亚少女是谁？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奈菲亚是什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关于米西利亚的现状</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关于边境公爵赛特拉斯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关于人类和艾莱亚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关于托瑞斯家族</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(返回)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你想知道些什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">怎么拾起和使用道具</t>
+  </si>
+  <si>
+    <t xml:space="preserve">采集和疲劳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">制造</t>
+  </si>
+  <si>
+    <t xml:space="preserve">战斗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">能力和魔法</t>
+  </si>
+  <si>
+    <t xml:space="preserve">饮食、睡眠、生活</t>
+  </si>
+  <si>
+    <t xml:space="preserve">视野和光源</t>
+  </si>
+  <si>
+    <t xml:space="preserve">首先教你如何拾取和使用道具吧。
+道具会有掉落在地面，和被安装在地面的两种状态。只要走到掉落在地面的道具上就可以将其自动捡起，而被安装好的家具之类的道具则需要用右键点击才能拿起来。
+手中拿着道具时，点击自己可以将道具收纳到背包中，右键点击地面则可以将手里的道具重新安装在指定位置。
+想拾起安装在城镇中的道具则需要偷窃的技术，不过现在还没有学习的必要吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点击屏幕右下方背包的标志就可以查看背包内容。可以用鼠标拖动的方式来自由移动背包内的道具。
+食物和书之类的道具可以通过右键点击直接使用。另外，用鼠标中键点击道具（或按下R键），可以显示对该道具能作的所有动作哦。
+你可以用鼠标滚轮快速切换屏幕下方的道具栏，把常用工具和消耗品放在快捷栏就可以更方便的使用。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目前自然资源就可以满足你的生活所需。野蘑菇和莓子都是宝贵的食物来源。等你熟练怎么砍伐树木和加工石材后就可以着手准备制作家具和建筑物的材料了。
+你可以试着用右键采集地图上的资源，但有些道具需要斧头或稿子来进行采集。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">采集等特定行为会消耗你的精力。精力过低时会进入疲劳状态，疲劳时生命值不再自然恢复。如果还要继续工作让精力进一步降低还会有失去意识的风险。
+恢复疲劳的方法比较有限，还请注意控制自己的精力状态。
+当你疲劳到举步难行的时候，在床上睡一觉就能恢复精力了。如果找不到床的话，就试试「休息」能力吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">使用篝火或制作台等设备，可以消耗身上的材料制造道具。
+一开始能造的东西很少，你可以通过开宝箱等方式得到新的配方，阅读之后就可以学会更多道具的制造方法。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">制造的时候除了背包中的素材，还可以使用储存在远处容器内的素材作为材料哦。不过你不可以使用安装在地上的素材和不属于你的素材。
+另外，如果制造道具所需的技能等级不足，就会极大增加精力的消耗。在制造高等级配方之前，先制造一些简单的道具锻炼手艺吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未完</t>
+  </si>
+  <si>
+    <t xml:space="preserve">能力
+能力和魔法有使用次数的限制。
+（未完）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">饮食
+空腹或困倦的时候会停止自愈（未完）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你说在森林中看到了艾莱亚的少女？
+当时你意识不太清楚，我想你看到的大概是和我们同行的伙伴菲亚玛吧。她还在这周围闲逛呢，就是她发现了你。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不过菲亚玛是人类，有很多人和你一样都搞错了。
+她…可以听到森林的声音。说到这个，刚才她也说了件奇怪的事…说是梦中的一名少女将把我们引至了此处。那究竟是什么意思啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">提里斯各地都散布着很多无人踏足的遗迹，我们将其称为「奈菲亚的遗迹」，据说奈菲亚的深处沉睡着古代的秘宝。如果你觉得自己本事还不够格，建议还是不要操之过急地去探索比较好。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">米西利亚位于北提里斯和南部山脉之间，是由老乔南公爵治理的领地。从很久以前起人类和艾莱亚就一同居住在这里。
+我们的主公赛特拉斯大人和芙琳大人在百年前作为异形之森的使者来到了此处，后来赛特拉斯大人就留在了人类世界之中成为两族共存的象征，也一直都受到领民的崇拜。
+米西利亚虽然说不上富饶，却是个充满希望的和平国度。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">然而，15年前的大战让米西利亚中的不同种族间的关系出现了裂痕。
+面对我们的求助，森之民们选择了沉默，他们对被帝国侵略的提里斯视而不见，这让人类对他们产生了强烈的不信任感。到后来象征着两种族和谐共存的米西利亚中再也不见当年的景象，只剩下两族之间的记恨与对立。
+赛特拉斯大人的声音已经无法传达到人民的耳边。米西利亚的的国民同胞之间开始争夺在荒芜土地上残存的麦穗。而邻国和议会的秃鹫们却都只在幸灾乐祸地观望着这一切。
+这就是这个国家的现状。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">也许米西利亚已经不再有希望，人类和艾莱亚携手前进的日子也不会再回来了。
+但，赛特拉斯大人还没有放弃。我也要为生养我的米西利亚…不，是为了赛特拉斯大人尽力到最后。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在提里斯边境的柳木堡有一位领主，他身为艾莱亚人成为君主，是尼米尔奇迹的英雄。我想你应该也听说过“边境公爵赛特拉斯”的名号吧？
+赛特拉斯大人虽然是异形之森…古老森林的居民，却选择了和芙琳大人共同留在米西利亚，支持着托瑞斯家族的每一代人和米西利亚。他充满智慧，受人崇敬。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">他在十年战争中的功绩依然让人记忆犹新。那天…那一天的光景仍然烙印在所有米西利亚领民的眼中。
+自从与芙琳大人分别之后，赛特拉斯大人就一直躺在床上，表现的沉默寡言。那天晚上，我在柳木堡的城墙上无可奈何地诅咒着在不断逼近米西利亚的萨伊拉飞艇。城堡中的大伙聚集起来商讨对策，这时…赛特拉斯大人竟离开了他自己的房间。他用艾莱亚的语言，悲伤地向天空述说了一句什么话语。
+接着我们就看到一道蓝光闪过尼米尔的天空。然后…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我很难描述当时发生的事情。闪着蓝色光芒的狂风，将萨伊拉飞艇瞬间卷毁。风暴离去之后，在场的人们都哑然无声，大伙都愣神的看着燃烧的飞艇慢慢坠落时发出的红光。赛特拉斯大人的脸上，留下了一道泪水。
+…失去了无敌的萨伊拉飞艇后，帝国开始从提里斯和各地撤退。这就是十年战争终结的经过。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾莱亚远在人类文明诞生之前就存在了。在上古世代，人类畏惧着拥有卓越知识和神秘力量的艾莱亚，将他们作为神崇拜，称艾莱亚为母亲。
+艾莱亚是美丽、和平且安详的种族。尽管他们教授了人类很多知识，但却从不会主动积极和人类有什么来往。他们住在蓝色的森林中，很少在人前现身。他们森林的树木会放出瘴气，拒绝着人类的入侵…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">就像你知道的那样，两个种族的关系并不好。人类对旁观十年战争的艾莱亚感到不满。也有人认为艾莱亚的存在妨碍了人类的独立和创造。
+但是，他们什么时候说过自己是人类的同盟者，或保护者呢？是人类擅自将他们称为母亲，又因为被他们忽视而感到愤怒。现在人类所做的事，不就是想通过大声呼喊不公好让自己对艾莱亚的依赖和迁怒正当化吗。
+然而大众并不知道，在推动憎恨声浪的背后一向都隐藏着某些为权力者的目的。呵呵，这里就该说欢迎来到人类的世界了吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赛特拉斯大人和芙琳大人，对于托瑞斯家族来说非常特别。对于我们来说，他们是看着我们长大的亲人，也是会在我们生命的尽头照料我们的司祭。是了解米西利亚和托瑞斯历史的教师，也是分享快乐和悲伤的朋友。
+乔南公爵…我的父亲，即使到了现在，他还是会在赛特拉斯大人面前笑得像个孩子。那是我和弟弟绝对无法看到的一面。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在宽敞而冰冷的米西利亚石造宫廷中，就算是血缘维系的兄弟，却也会偶尔感觉彼此像是陌生人一样。但赛特拉斯大人和芙琳大人之间不会那样，所以我从小就被他们亲密无间、互相支持的模样深深吸引。
+…你想笑我也无所谓。但，只要有赛特拉斯大人和芙琳大人在的地方，就总是充满了和谐。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在这么大的土地上，无论想干什么都需要人手。
+增加居民的方式有很多。可以饲养野生动物，旅途中也可能会有意想不到的邂逅。另外这个大陆的某处似乎有奴隶商人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不过，最简单的方式就是从告示板上雇佣移居志愿者了呢。
+雇佣居民需要被称为灯火的资源。每天的结束时都会得到一些灯火，如果不着急的话用累积的灯火雇佣居民会是个很稳定的方式。
+那就让我来看看你的本事吧。无论用什么方式都好，找个新居民来吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好像找到新同伴了呢。这一定会对开拓土地有所帮助。
+你还可以邀请居民加入队伍一起冒险哦。不过，这样一来同行的居民就不能完成家园里的工作了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那么，今后的开拓和冒险也需要更多人手。我给你定一个家园发展的目标吧。
+目标是，「招募十个居民」。
+也许会花不少时间，完成后记得向我报告。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这地方热闹了不少啊。看来向米西利亚的主公汇报的日子不远了。
+这个卷轴就是达成目标的报酬。这是可以追溯伊尔瓦大地记忆召唤居民的贵重品。要好好使用啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这件事对鼓足干劲开拓新天地的你来说确实有些残酷…但早晚你会知道的。
+首先这片土地当然是属于你的，随便你怎么使用都没关系。只不过，这片土地在米西利亚的领土内，这片土地的所有资产连每一匹家畜都必须记录在税务登记本上，
+你会定期收到税金账单。如果有人滞纳税金，那等待着他的将会是凄惨的命运。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…不过嘛，那是之后的事情了。现在无需担心，专心开拓吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">终于收到了税金账单啊。
+那么让我在这里说明纳税的方法。支付的方式倒是很简单，没什么好担心的。问题在于，怎么准备这笔钱。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拿到税金账单之后，就去米西利亚首都吧。首都的市政厅里放着纳税箱，带上足够的钱，把税金账单放进去就可以了。
+办完这件要紧事后心情也会放松不少吧。不如在纳完税后顺便物色一下米西利亚市场的特产怎么样？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不止是税金，你将来也会收到各种名目的账单。放宽心，支付方式都是一样的。不过，还是要留意支付期限。滞纳账单的话不仅会降低你的评价，市政厅的家伙们也不介意使用武力。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊对了，有件重要的事情忘了告诉你。向东南方向沿着路走就能到米西利亚。距离稍微有点远，不要迷路啦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">怎么，初次纳税很紧张吗？
+缴税本身并不是很难啦。上次已经说过，问题是怎么准备那些钱。
+给纳完税的你一个不错的礼物吧。只要安装好「邮箱」就能自动收纳送到家园的信和账单，是个很方便的家具。这样一来你就不会错过重要的信息了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在我跟你说明议会有关的事情之前，要先讲讲无聊的历史。
+与东边纷争不绝的艾索里亚相比，北提里斯一直都是片和平的大陆。就算是有萨伊拉飞艇的帝国，也很少踏足这片远隔艾索里亚海的大陆。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但随着新王国耶鲁和帝国之间的摩擦加剧，两国之间的争斗终于让战火洒向了整个世界。提里斯诸国认为有必要联合起来结束这场战争，于是在提里斯和平与繁荣的旗帜下就成立了提里斯联盟。
+联盟提交的议案会在提里斯议会上审议。虽说是议案，但从国家之间的大事到村落援助的小事都有所涉及。而决定议案通过与否的投票权就在议员们的手中。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你在旅途中也许会遇到议会的议员。和他们混个脸熟，得到议会的支持，对家园发展也是非常重要的。
+找到议员后，就先去搭个话吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">北提里斯很广阔。熟悉这里的生活之后，就去四处探索一下吧。
+在东南方向，有个叫做尼米尔的洞窟。洞窟的浅层应该没有很危险的魔物。其实我也对那洞窟有些兴趣，你可以帮忙调查一下吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在出门探索之前，我要把这卷轴交给你。
+只要阅读「脱离卷轴」就可以离开奈菲亚回到地面。
+阅读「归还卷轴」可以让你传送到去过的奈菲亚的最下层或家园。
+它们都是对冒险大有用处的道具。还请好好使用。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你回来了吗。我正担心菲亚突然不见了呢。虽然她经常自己跑去其他地方…
+嗯，先不说这个。让我听听你的报告吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">巨大的…蛾子…？你库莱姆吸多了吧？
+不好意思，这听起来确实让人难以置信，不过既然两个人都看到了，那应该也不是幻觉呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我们寻找的神秘力量，其实是沉睡在地底的以太结晶吗。如果森之淑女欧涅芙说的是真的，那意味着东南方的利萨纳斯遗迹中也沉睡着一个魔石。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虽然不该轻易相信欧涅芙这种古老存在的话，但我们确实没有其他的选择了。
+利萨纳斯吗…看来有必要去调查一下呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…我还有一件在意的事情。
+你说你见到的人里有一个脖子上纹有没品位纹身的男人？这个人可能是…不，那种家伙找遍提里斯也不会有第二个。
+他肯定是埃夫隆德·托瑞斯。他是米西利亚公爵乔南·托瑞斯的儿子，也是我不成器的弟弟。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">别表现得这么惊讶啊。我已经和托瑞斯家断绝关系了。现在不过是侍奉赛特拉斯大人的一个间谍而已。
+不过话说回来了，埃夫隆德好歹是米西利亚的继承者，怎么会和帝国的人在一起？
+只给人一种不好的预感啊，不过这是我的私事。你就去继续搜集利萨纳斯的情报吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…救你的时候还以为是白费力气，没想到还真是一场奇妙的邂逅。多亏了你，我也听到不少新情报。
+我们要回到柳木堡向赛特拉斯大人进行报告。相处时间不长，也多谢你的帮忙了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果…你对探索利萨纳斯有兴趣的话，不如也来柳木堡一趟吧？
+当然不是强制的。你可以留在这继续发展你的据点，也可以去游历各地长长见识。如何看待这世界，如何留下自己的足迹，都取决于你自己的决定。
+愿你得到风的加护。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">制造是生活和冒险都不可或缺的技术。
+我算不上是专业的，不过会尽己所能地教你。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好，首先就从制作台开始吧。制作台是制造的基础设施，使用制作台就能立刻制造地板或墙壁了。
+你只要使用已经学会的「简易制造」能力就可以直接制造制作台了。你就先去砍伐一下那边的树来准备原木，然后试着用「简易制造」造个制作台出来吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没错没错，接下来只需要把完成的制作台安装到合适的地面上就可以了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">做得还不错。
+你试着用过制作台了吗？虽然一开始能做的东西很少，但只要得到新的配方，就可以造更多道具了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这样一来就做好盖房子的准备了，但在这之前，先准备好夜晚的光源比较好。
+只要有光源，就可以在夜晚看到更远的地方。在周围收集素材，用制作台制造「火把」吧。
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">制造「火把」所需的「细绳」要在制作台用「藤蔓」制造。造好火把之后，别忘了把它装备在光源栏上。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好，这样你就踏出了制造者的第一步。要学的东西还有很多，我给你定一个目标吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目标是「在这片土地上独立建造一栋房子」。
+听起来很麻烦，但只要四面用墙围住再装个门，就可以称为房子了。我去给你准备一些新房贺礼，你就加油盖房子吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看起来你盖好房子了啊，恭喜，这样一来就不用风餐露宿了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">让我来介绍一下房子的用处吧。
+你建造的房子外观和功能，都可以使用建筑告示板来定制。另外，用墙壁分割房子里的空间就可以划分房间，建筑告示板可以用来定制任意一个房间。
+这些建筑牌和房间牌就是我送你的礼物。虽然不算贵重，还请试着定制你的新房子吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在这世道下，学一两种武器的用法一定会派上用场。
+在野外遭遇的大部分生物只要看到你就会攻过来。在装备不齐全的现在，你最好用鼠标悬停在敌人身上查看一下敌人的强度，从而避开和那些强敌战斗。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">首先要进行的是简单的实战训练。我在告示板后面绑了个路过的朋克。被拘束的敌人无法移动，如果觉得危险你可以随时退到安全的距离恢复体力。
+别客气，来尽情揍这个朋克吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">做得好。
+像朋克这种脑袋不灵活的敌人只会用一些简单的攻击手段，没什么好怕的。相对的，你要格外小心使用远程武器的敌人，还有那些和你直接接触后会使出不妙的特殊能力的敌人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接下来的训练对手是野猪。还是一样绑在告示板后面了。
+野猪和朋克一样都是简单的对手，但可不要小瞧野生动物的战斗能力。近距离硬碰硬的话也有可能会吃亏。
+对付这样的敌人可以用远程攻击。我会给你一些道具，试着花点工夫打倒它吧。别忘了你可以「投掷」道具。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">了不起。这样一来你就会处理那些只会靠蛮力近战的敌人了。
+像野猪这样的对手还算比较容易对付，但如果被它们围住，或被阻断退路，可能也会栽了跟头。无论何时都不要太过自信，一定要准备好随时脱离战斗的手段。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">为了进一步的锻炼，我给你定个目标吧。
+目标就是「打倒一百个敌人」。
+别担心，现在的北提里斯到处都是危险的魔物和恶人。很容易就能遇到一两百个敌人了。至今为止打倒的敌人数量会记录在日志中，忘记的话就看看吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">做得很棒。看来你已经可以保护自己了。
+要学的东西还有很多，但你该做的是继续增加实战的经验。这些白金币就是给你的报酬。
+把白金币交给城里的技能训练师就可以锻炼已有技能，也可以用来学习新技能哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">为了进一步在这片土地上强化你的据点，必须了解什么是「公用容器」才行。
+公用容器是居民生活和工作不可或缺的设备。我只教一次，要仔细记好！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">木箱和桶之类的容器有「权限」这样的概念。一般来说，你安装的容器只有你可以取用里面的道具，但只要点击容器右侧的「锁」图标，就可以将它变成公用容器。
+公用容器可以供居民和队伍成员使用。肚子饿的人会从容器中找食物，看到好装备后就会拿走。如果有工作需要的素材，也会从容器中自取。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">另外，居民会往公用容器中交付发现的物资和工作的产出物，所以要常常查看公用容器的剩余容量。
+你这次的报酬是这个「木箱」。把它安装在地面上，试着变更为「公用容器」吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已经安装好公用容器了啊。
+变更容器设定，可以做出优先使用的容器，或只放入特定物品的容器。土地开发后需要整理据点内物资的话，就试试这个方法吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你来得正是时候。
+有件事情没和你说过，按规定米西利亚会往开拓地派遣开拓监察官。监察官这个名字有些严肃，但不需要担心。把他当成帮助拓荒的帮手就好。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不过嘛，如果你嫌麻烦想自由生活的话，我也可以代替你和米西利亚交涉让他们不派遣监察官过来。
+选择权在你，打算怎么办？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我需要开拓监察官的帮助</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想自由生活</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是吗。我就知道你会这么想，所以已经为了你的开拓地找了一位优秀的监察官。他是我的熟人，虽然性格有点难搞，但工作上无可挑剔。
+让我来介绍吧，我的朋友，也是米西利亚最好的开拓监察官，罗伊特尔。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…这是怎么回事？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我听你说这里是「以后金币会堆积如山的很有潜力的开拓地」，所以才来看看…难道我听错了？
+这地方连地面都没整平，不就是个破荒地吗！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阿什兰德，你必须给我解释清楚。我可是很忙的。你叫我来这到处是荒草和岩石的未开发地做什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呼，看来旅途的疲惫让你忽视了眼前的宝藏啊，罗伊特尔。黄金矿石并不一定只会躺在地上。
+如你所说，这里确实只是片荒地而已。但你看到我旁边这位冒险者了吗？#he才是我叫你来此的理由。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你说这呆头呆脑的冒险者，是金矿石？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…嗯，没错。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…哼，既然你说到了这份上，那我就试试好了。不看好归不看好，我也确实欠你和菲亚不少人情。
+不过啊，唉，这就只是个什么都没有的荒草地。一般来说搞拓荒之前应该做一定的准备才对吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咳哼…啊…那边那位冒险者。总之就是这么回事，以后就由我来担任你的开拓监察官了。
+那我也重新自我介绍一下吧。我叫罗伊特尔。是米西利亚最高级开拓监察官，也是米西利亚宫廷顾问兼宫廷财务官。最喜欢高级奥尔维纳红酒和高效的开拓计划，讨厌的东西是无能的开拓者。
+只要有我的经验和知识，这片开拓地必然会成功。当然这也取决于你的努力。总而言之，好好干吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">罗伊特尔是个严格又认真的男人。一定会对你的开拓发展有很大帮助。
+如果对家园的运营和提里斯生活有疑问，就找他谈谈吧、</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好吧。如果你是这么想的，那就随心所欲吧。如果改变主意的话，也可以随时告诉我。</t>
+  </si>
 </sst>
 </file>
 
@@ -1456,52 +1909,52 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -1541,7 +1994,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1550,78 +2003,78 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1635,13 +2088,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -1817,26 +2270,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L373"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
+    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1874,23 +2327,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>125</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="E8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1898,7 +2351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1906,7 +2359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1914,7 +2367,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
@@ -1922,16 +2375,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="C16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="I16" s="1">
         <v>117</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -1940,15 +2393,18 @@
       <c r="K16" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L16" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="17" ht="13.8">
       <c r="C17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="1">
         <v>118</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -1957,12 +2413,15 @@
       <c r="K17" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L17" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="18" ht="64.15">
       <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="J18" s="4" t="s">
@@ -1971,12 +2430,15 @@
       <c r="K18" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L18" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="B21" s="1" t="s">
         <v>32</v>
       </c>
@@ -1986,7 +2448,7 @@
       <c r="E21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I21" s="1" t="n">
+      <c r="I21" s="1">
         <v>2</v>
       </c>
       <c r="J21" s="1" t="s">
@@ -1995,8 +2457,11 @@
       <c r="K21" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L21" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="22" ht="12.8">
       <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
@@ -2006,7 +2471,7 @@
       <c r="E22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="1" t="n">
+      <c r="I22" s="1">
         <v>3</v>
       </c>
       <c r="J22" s="1" t="s">
@@ -2015,15 +2480,18 @@
       <c r="K22" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L22" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="23" ht="12.8">
       <c r="B23" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="1" t="n">
+      <c r="I23" s="1">
         <v>4</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2032,15 +2500,18 @@
       <c r="K23" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L23" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="24" ht="12.8">
       <c r="B24" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="1" t="n">
+      <c r="I24" s="1">
         <v>5</v>
       </c>
       <c r="J24" s="1" t="s">
@@ -2049,8 +2520,11 @@
       <c r="K24" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L24" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="25" ht="12.8">
       <c r="E25" s="1" t="s">
         <v>47</v>
       </c>
@@ -2058,22 +2532,22 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="12.8">
       <c r="E26" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="E27" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.8">
       <c r="A29" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="12.8">
       <c r="E30" s="1" t="s">
         <v>51</v>
       </c>
@@ -2081,8 +2555,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I31" s="1" t="n">
+    <row r="31" ht="95.5">
+      <c r="I31" s="1">
         <v>6</v>
       </c>
       <c r="J31" s="4" t="s">
@@ -2091,8 +2565,11 @@
       <c r="K31" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="32" ht="12.8">
       <c r="E32" s="1" t="s">
         <v>55</v>
       </c>
@@ -2100,7 +2577,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.8">
       <c r="E33" s="1" t="s">
         <v>57</v>
       </c>
@@ -2108,7 +2585,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="B34" s="1" t="s">
         <v>13</v>
       </c>
@@ -2116,13 +2593,13 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="A36" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I37" s="1" t="n">
+    <row r="37" ht="53.7">
+      <c r="I37" s="1">
         <v>7</v>
       </c>
       <c r="J37" s="4" t="s">
@@ -2131,8 +2608,11 @@
       <c r="K37" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L37" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="38" ht="12.8">
       <c r="E38" s="1" t="s">
         <v>55</v>
       </c>
@@ -2140,8 +2620,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I39" s="1" t="n">
+    <row r="39" ht="95.5">
+      <c r="I39" s="1">
         <v>8</v>
       </c>
       <c r="J39" s="4" t="s">
@@ -2150,8 +2630,11 @@
       <c r="K39" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L39" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="40" ht="12.8">
       <c r="E40" s="1" t="s">
         <v>65</v>
       </c>
@@ -2159,8 +2642,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I41" s="1" t="n">
+    <row r="41" ht="12.8">
+      <c r="I41" s="1">
         <v>9</v>
       </c>
       <c r="J41" s="1" t="s">
@@ -2169,8 +2652,11 @@
       <c r="K41" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
       <c r="E42" s="1" t="s">
         <v>65</v>
       </c>
@@ -2178,8 +2664,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I43" s="1" t="n">
+    <row r="43" ht="22.35">
+      <c r="I43" s="1">
         <v>10</v>
       </c>
       <c r="J43" s="4" t="s">
@@ -2188,8 +2674,11 @@
       <c r="K43" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L43" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="44" ht="12.8">
       <c r="E44" s="1" t="s">
         <v>51</v>
       </c>
@@ -2197,7 +2686,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="12.8">
       <c r="B45" s="1" t="s">
         <v>13</v>
       </c>
@@ -2205,13 +2694,13 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="A48" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="103.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I49" s="1" t="n">
+    <row r="49" ht="103.7">
+      <c r="I49" s="1">
         <v>11</v>
       </c>
       <c r="J49" s="5" t="s">
@@ -2220,9 +2709,12 @@
       <c r="K49" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I50" s="1" t="n">
+      <c r="L49" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="50" ht="68.65">
+      <c r="I50" s="1">
         <v>12</v>
       </c>
       <c r="J50" s="6" t="s">
@@ -2231,9 +2723,12 @@
       <c r="K50" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I51" s="1" t="n">
+      <c r="L50" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="51" ht="12.8">
+      <c r="I51" s="1">
         <v>13</v>
       </c>
       <c r="J51" s="1" t="s">
@@ -2242,19 +2737,22 @@
       <c r="K51" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L51" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="52" ht="12.8">
       <c r="B52" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="12.8">
       <c r="A54" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I55" s="1" t="n">
+    <row r="55" ht="116.4">
+      <c r="I55" s="1">
         <v>14</v>
       </c>
       <c r="J55" s="4" t="s">
@@ -2263,17 +2761,20 @@
       <c r="K55" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L55" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="56" ht="12.8">
       <c r="B56" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" ht="12.8">
       <c r="A60" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I60" s="1" t="n">
+      <c r="I60" s="1">
         <v>15</v>
       </c>
       <c r="J60" s="1" t="s">
@@ -2282,15 +2783,18 @@
       <c r="K60" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L60" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="61" ht="12.8">
       <c r="B61" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I61" s="1" t="n">
+      <c r="I61" s="1">
         <v>16</v>
       </c>
       <c r="J61" s="1" t="s">
@@ -2299,15 +2803,18 @@
       <c r="K61" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L61" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="62" ht="12.8">
       <c r="B62" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I62" s="1" t="n">
+      <c r="I62" s="1">
         <v>124</v>
       </c>
       <c r="J62" s="1" t="s">
@@ -2316,8 +2823,11 @@
       <c r="K62" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L62" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="63" ht="12.8">
       <c r="B63" s="1" t="s">
         <v>90</v>
       </c>
@@ -2327,7 +2837,7 @@
       <c r="E63" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I63" s="1" t="n">
+      <c r="I63" s="1">
         <v>18</v>
       </c>
       <c r="J63" s="1" t="s">
@@ -2336,8 +2846,11 @@
       <c r="K63" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L63" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="64" ht="12.8">
       <c r="B64" s="1" t="s">
         <v>94</v>
       </c>
@@ -2347,7 +2860,7 @@
       <c r="E64" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I64" s="1" t="n">
+      <c r="I64" s="1">
         <v>19</v>
       </c>
       <c r="J64" s="1" t="s">
@@ -2356,8 +2869,11 @@
       <c r="K64" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L64" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="65" ht="12.8">
       <c r="B65" s="1" t="s">
         <v>97</v>
       </c>
@@ -2367,7 +2883,7 @@
       <c r="E65" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I65" s="1" t="n">
+      <c r="I65" s="1">
         <v>20</v>
       </c>
       <c r="J65" s="1" t="s">
@@ -2376,8 +2892,11 @@
       <c r="K65" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L65" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="66" ht="12.8">
       <c r="B66" s="1" t="s">
         <v>100</v>
       </c>
@@ -2387,7 +2906,7 @@
       <c r="E66" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I66" s="1" t="n">
+      <c r="I66" s="1">
         <v>21</v>
       </c>
       <c r="J66" s="1" t="s">
@@ -2396,15 +2915,18 @@
       <c r="K66" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L66" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="67" ht="12.8">
       <c r="B67" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I67" s="1" t="n">
+      <c r="I67" s="1">
         <v>22</v>
       </c>
       <c r="J67" s="1" t="s">
@@ -2413,8 +2935,11 @@
       <c r="K67" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L67" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="68" ht="12.8">
       <c r="B68" s="1" t="s">
         <v>13</v>
       </c>
@@ -2422,13 +2947,13 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="12.8">
       <c r="A73" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I74" s="1" t="n">
+    <row r="74" ht="12.8">
+      <c r="I74" s="1">
         <v>23</v>
       </c>
       <c r="J74" s="1" t="s">
@@ -2437,15 +2962,18 @@
       <c r="K74" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L74" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="75" ht="12.8">
       <c r="B75" s="1" t="s">
         <v>108</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I75" s="1" t="n">
+      <c r="I75" s="1">
         <v>24</v>
       </c>
       <c r="J75" s="1" t="s">
@@ -2454,8 +2982,11 @@
       <c r="K75" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L75" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="76" ht="12.8">
       <c r="B76" s="1" t="s">
         <v>111</v>
       </c>
@@ -2465,7 +2996,7 @@
       <c r="E76" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I76" s="1" t="n">
+      <c r="I76" s="1">
         <v>25</v>
       </c>
       <c r="J76" s="1" t="s">
@@ -2474,8 +3005,11 @@
       <c r="K76" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L76" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="77" ht="12.8">
       <c r="B77" s="1" t="s">
         <v>115</v>
       </c>
@@ -2485,7 +3019,7 @@
       <c r="E77" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I77" s="1" t="n">
+      <c r="I77" s="1">
         <v>26</v>
       </c>
       <c r="J77" s="1" t="s">
@@ -2494,8 +3028,11 @@
       <c r="K77" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L77" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="78" ht="12.8">
       <c r="B78" s="1" t="s">
         <v>119</v>
       </c>
@@ -2505,7 +3042,7 @@
       <c r="E78" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I78" s="1" t="n">
+      <c r="I78" s="1">
         <v>27</v>
       </c>
       <c r="J78" s="1" t="s">
@@ -2514,8 +3051,11 @@
       <c r="K78" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L78" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="79" ht="12.8">
       <c r="B79" s="1" t="s">
         <v>123</v>
       </c>
@@ -2525,7 +3065,7 @@
       <c r="E79" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I79" s="1" t="n">
+      <c r="I79" s="1">
         <v>28</v>
       </c>
       <c r="J79" s="1" t="s">
@@ -2534,8 +3074,11 @@
       <c r="K79" s="1" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L79" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="80" ht="12.8">
       <c r="B80" s="1" t="s">
         <v>127</v>
       </c>
@@ -2545,7 +3088,7 @@
       <c r="E80" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I80" s="1" t="n">
+      <c r="I80" s="1">
         <v>29</v>
       </c>
       <c r="J80" s="1" t="s">
@@ -2554,8 +3097,11 @@
       <c r="K80" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L80" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="81" ht="12.8">
       <c r="B81" s="1" t="s">
         <v>131</v>
       </c>
@@ -2565,7 +3111,7 @@
       <c r="E81" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I81" s="1" t="n">
+      <c r="I81" s="1">
         <v>30</v>
       </c>
       <c r="J81" s="1" t="s">
@@ -2574,15 +3120,18 @@
       <c r="K81" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L81" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="82" ht="12.8">
       <c r="B82" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I82" s="1" t="n">
+      <c r="I82" s="1">
         <v>31</v>
       </c>
       <c r="J82" s="1" t="s">
@@ -2591,8 +3140,11 @@
       <c r="K82" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L82" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="83" ht="12.8">
       <c r="B83" s="1" t="s">
         <v>13</v>
       </c>
@@ -2600,8 +3152,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I84" s="1" t="n">
+    <row r="84" ht="12.8">
+      <c r="I84" s="1">
         <v>32</v>
       </c>
       <c r="J84" s="1" t="s">
@@ -2610,13 +3162,16 @@
       <c r="K84" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L84" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="85" ht="12.8">
       <c r="A85" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" ht="12.8">
       <c r="C86" s="1" t="s">
         <v>135</v>
       </c>
@@ -2627,8 +3182,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I87" s="1" t="n">
+    <row r="87" ht="126.85">
+      <c r="I87" s="1">
         <v>33</v>
       </c>
       <c r="J87" s="4" t="s">
@@ -2637,9 +3192,12 @@
       <c r="K87" s="4" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I88" s="1" t="n">
+      <c r="L87" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="88" ht="116.4">
+      <c r="I88" s="1">
         <v>34</v>
       </c>
       <c r="J88" s="4" t="s">
@@ -2648,8 +3206,11 @@
       <c r="K88" s="4" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L88" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="89" ht="12.8">
       <c r="B89" s="1" t="s">
         <v>41</v>
       </c>
@@ -2657,12 +3218,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" ht="12.8">
       <c r="A91" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" ht="12.8">
       <c r="C92" s="1" t="s">
         <v>141</v>
       </c>
@@ -2673,8 +3234,8 @@
         <v>142</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I93" s="1" t="n">
+    <row r="93" ht="85.05">
+      <c r="I93" s="1">
         <v>35</v>
       </c>
       <c r="J93" s="4" t="s">
@@ -2683,9 +3244,12 @@
       <c r="K93" s="4" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="94" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I94" s="1" t="n">
+      <c r="L93" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="94" ht="95.5">
+      <c r="I94" s="1">
         <v>36</v>
       </c>
       <c r="J94" s="4" t="s">
@@ -2694,8 +3258,11 @@
       <c r="K94" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L94" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="95" ht="12.8">
       <c r="B95" s="1" t="s">
         <v>41</v>
       </c>
@@ -2703,12 +3270,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" ht="12.8">
       <c r="A97" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" ht="12.8">
       <c r="C98" s="1" t="s">
         <v>147</v>
       </c>
@@ -2719,8 +3286,8 @@
         <v>148</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I99" s="1" t="n">
+    <row r="99" ht="64.15">
+      <c r="I99" s="1">
         <v>37</v>
       </c>
       <c r="J99" s="4" t="s">
@@ -2729,9 +3296,12 @@
       <c r="K99" s="4" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="100" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I100" s="1" t="n">
+      <c r="L99" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="100" ht="74.6">
+      <c r="I100" s="1">
         <v>38</v>
       </c>
       <c r="J100" s="4" t="s">
@@ -2740,8 +3310,11 @@
       <c r="K100" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L100" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="101" ht="12.8">
       <c r="B101" s="1" t="s">
         <v>41</v>
       </c>
@@ -2749,12 +3322,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" ht="12.8">
       <c r="A104" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" ht="12.8">
       <c r="C105" s="1" t="s">
         <v>153</v>
       </c>
@@ -2765,8 +3338,8 @@
         <v>154</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I106" s="1" t="n">
+    <row r="106" ht="12.8">
+      <c r="I106" s="1">
         <v>39</v>
       </c>
       <c r="J106" s="1" t="s">
@@ -2775,8 +3348,11 @@
       <c r="K106" s="1" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L106" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="107" ht="12.8">
       <c r="B107" s="1" t="s">
         <v>41</v>
       </c>
@@ -2784,12 +3360,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" ht="12.8">
       <c r="A109" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" ht="12.8">
       <c r="C110" s="1" t="s">
         <v>157</v>
       </c>
@@ -2800,8 +3376,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I111" s="1" t="n">
+    <row r="111" ht="53.7">
+      <c r="I111" s="1">
         <v>40</v>
       </c>
       <c r="J111" s="4" t="s">
@@ -2810,23 +3386,26 @@
       <c r="K111" s="1" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L111" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="112" ht="12.8">
       <c r="E112" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" ht="12.8">
       <c r="B113" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" ht="12.8">
       <c r="A115" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" ht="12.8">
       <c r="C116" s="1" t="s">
         <v>160</v>
       </c>
@@ -2837,8 +3416,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I117" s="1" t="n">
+    <row r="117" ht="32.8">
+      <c r="I117" s="1">
         <v>41</v>
       </c>
       <c r="J117" s="4" t="s">
@@ -2847,23 +3426,26 @@
       <c r="K117" s="1" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L117" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="118" ht="12.8">
       <c r="E118" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" ht="12.8">
       <c r="B119" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" ht="12.8">
       <c r="A121" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" ht="12.8">
       <c r="C122" s="1" t="s">
         <v>163</v>
       </c>
@@ -2874,8 +3456,8 @@
         <v>164</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I123" s="1" t="n">
+    <row r="123" ht="12.8">
+      <c r="I123" s="1">
         <v>42</v>
       </c>
       <c r="J123" s="1" t="s">
@@ -2884,22 +3466,25 @@
       <c r="K123" s="1" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L123" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="124" ht="12.8">
       <c r="E124" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" ht="12.8">
       <c r="B125" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" ht="43.25">
       <c r="A134" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I134" s="1" t="n">
+      <c r="I134" s="1">
         <v>43</v>
       </c>
       <c r="J134" s="4" t="s">
@@ -2908,9 +3493,12 @@
       <c r="K134" s="4" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="135" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I135" s="1" t="n">
+      <c r="L134" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="135" ht="53.7">
+      <c r="I135" s="1">
         <v>44</v>
       </c>
       <c r="J135" s="4" t="s">
@@ -2919,19 +3507,22 @@
       <c r="K135" s="4" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L135" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="136" ht="12.8">
       <c r="B136" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" ht="12.8">
       <c r="A138" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I139" s="1" t="n">
+    <row r="139" ht="53.7">
+      <c r="I139" s="1">
         <v>45</v>
       </c>
       <c r="J139" s="4" t="s">
@@ -2940,19 +3531,22 @@
       <c r="K139" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L139" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="140" ht="12.8">
       <c r="B140" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" ht="12.8">
       <c r="A142" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I143" s="1" t="n">
+    <row r="143" ht="116.4">
+      <c r="I143" s="1">
         <v>47</v>
       </c>
       <c r="J143" s="4" t="s">
@@ -2961,9 +3555,12 @@
       <c r="K143" s="4" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="144" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I144" s="1" t="n">
+      <c r="L143" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="144" ht="158.2">
+      <c r="I144" s="1">
         <v>48</v>
       </c>
       <c r="J144" s="4" t="s">
@@ -2972,9 +3569,12 @@
       <c r="K144" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="145" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I145" s="1" t="n">
+      <c r="L144" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="145" ht="64.15">
+      <c r="I145" s="1">
         <v>49</v>
       </c>
       <c r="J145" s="4" t="s">
@@ -2983,19 +3583,22 @@
       <c r="K145" s="4" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L145" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="146" ht="12.8">
       <c r="B146" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" ht="12.8">
       <c r="A148" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I149" s="1" t="n">
+    <row r="149" ht="74.6">
+      <c r="I149" s="1">
         <v>50</v>
       </c>
       <c r="J149" s="4" t="s">
@@ -3004,9 +3607,12 @@
       <c r="K149" s="4" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="150" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I150" s="1" t="n">
+      <c r="L149" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="150" ht="137.3">
+      <c r="I150" s="1">
         <v>51</v>
       </c>
       <c r="J150" s="4" t="s">
@@ -3015,9 +3621,12 @@
       <c r="K150" s="4" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="151" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I151" s="1" t="n">
+      <c r="L150" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="151" ht="105.95">
+      <c r="I151" s="1">
         <v>52</v>
       </c>
       <c r="J151" s="4" t="s">
@@ -3026,19 +3635,22 @@
       <c r="K151" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L151" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="152" ht="12.8">
       <c r="B152" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" ht="12.8">
       <c r="A156" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I157" s="1" t="n">
+    <row r="157" ht="105.95">
+      <c r="I157" s="1">
         <v>53</v>
       </c>
       <c r="J157" s="4" t="s">
@@ -3047,9 +3659,12 @@
       <c r="K157" s="4" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="158" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I158" s="1" t="n">
+      <c r="L157" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="158" ht="147.75">
+      <c r="I158" s="1">
         <v>54</v>
       </c>
       <c r="J158" s="4" t="s">
@@ -3058,19 +3673,22 @@
       <c r="K158" s="4" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L158" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="160" ht="12.8">
       <c r="B160" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" ht="12.8">
       <c r="A162" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I163" s="1" t="n">
+    <row r="163" ht="85.05">
+      <c r="I163" s="1">
         <v>55</v>
       </c>
       <c r="J163" s="4" t="s">
@@ -3079,9 +3697,12 @@
       <c r="K163" s="4" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="164" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I164" s="1" t="n">
+      <c r="L163" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="164" ht="64.15">
+      <c r="I164" s="1">
         <v>56</v>
       </c>
       <c r="J164" s="4" t="s">
@@ -3090,18 +3711,21 @@
       <c r="K164" s="1" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L164" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="166" ht="12.8">
       <c r="B166" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" ht="12.8">
       <c r="A172" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" ht="12.8">
       <c r="E173" s="1" t="s">
         <v>192</v>
       </c>
@@ -3109,38 +3733,44 @@
         <v>193</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" ht="12.8">
       <c r="E174" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" ht="12.8">
       <c r="E175" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" ht="12.8">
       <c r="A181" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I183" s="1" t="n">
+    <row r="183" ht="53.7">
+      <c r="I183" s="1">
         <v>57</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="184" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I184" s="1" t="n">
+      <c r="L183" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="184" ht="85.05">
+      <c r="I184" s="1">
         <v>58</v>
       </c>
       <c r="J184" s="4" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L184" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="185" ht="12.8">
       <c r="E185" s="1" t="s">
         <v>199</v>
       </c>
@@ -3148,71 +3778,80 @@
         <v>200</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" ht="12.8">
       <c r="E186" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" ht="12.8">
       <c r="A188" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I189" s="1" t="n">
+    <row r="189" ht="53.7">
+      <c r="I189" s="1">
         <v>59</v>
       </c>
       <c r="J189" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="190" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I190" s="1" t="n">
+      <c r="L189" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="190" ht="64.15">
+      <c r="I190" s="1">
         <v>60</v>
       </c>
       <c r="J190" s="4" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L190" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="191" ht="12.8">
       <c r="E191" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" ht="12.8">
       <c r="A192" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I193" s="1" t="n">
+    <row r="193" ht="53.7">
+      <c r="I193" s="1">
         <v>61</v>
       </c>
       <c r="J193" s="4" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L193" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="194" ht="12.8">
       <c r="E194" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" ht="12.8">
       <c r="E195" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" ht="12.8">
       <c r="A197" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" ht="12.8">
       <c r="J199" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" ht="12.8">
       <c r="E200" s="1" t="s">
         <v>199</v>
       </c>
@@ -3220,33 +3859,33 @@
         <v>208</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" ht="12.8">
       <c r="E201" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" ht="12.8">
       <c r="A203" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" ht="12.8">
       <c r="J205" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" ht="12.8">
       <c r="E206" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" ht="12.8">
       <c r="A208" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I209" s="1" t="n">
+    <row r="209" ht="124.6">
+      <c r="I209" s="1">
         <v>62</v>
       </c>
       <c r="J209" s="4" t="s">
@@ -3255,9 +3894,12 @@
       <c r="K209" s="6" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I210" s="1" t="n">
+      <c r="L209" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="210" ht="12.8">
+      <c r="I210" s="1">
         <v>63</v>
       </c>
       <c r="J210" s="1" t="s">
@@ -3266,8 +3908,11 @@
       <c r="K210" s="1" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L210" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="211" ht="12.8">
       <c r="E211" s="1" t="s">
         <v>199</v>
       </c>
@@ -3275,18 +3920,18 @@
         <v>216</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" ht="12.8">
       <c r="E212" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" ht="12.8">
       <c r="A214" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I216" s="1" t="n">
+    <row r="216" ht="53.7">
+      <c r="I216" s="1">
         <v>64</v>
       </c>
       <c r="J216" s="4" t="s">
@@ -3295,9 +3940,12 @@
       <c r="K216" s="4" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="217" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I217" s="1" t="n">
+      <c r="L216" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="217" ht="74.6">
+      <c r="I217" s="1">
         <v>65</v>
       </c>
       <c r="J217" s="4" t="s">
@@ -3306,9 +3954,12 @@
       <c r="K217" s="4" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I218" s="1" t="n">
+      <c r="L217" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="218" ht="12.8">
+      <c r="I218" s="1">
         <v>66</v>
       </c>
       <c r="J218" s="1" t="s">
@@ -3317,9 +3968,12 @@
       <c r="K218" s="1" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I219" s="1" t="n">
+      <c r="L218" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="219" ht="12.8">
+      <c r="I219" s="1">
         <v>67</v>
       </c>
       <c r="J219" s="1" t="s">
@@ -3328,24 +3982,27 @@
       <c r="K219" s="1" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L219" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="220" ht="12.8">
       <c r="E220" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" ht="12.8">
       <c r="A221" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" ht="12.8">
       <c r="E222" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I223" s="1" t="n">
+    <row r="223" ht="105.95">
+      <c r="I223" s="1">
         <v>68</v>
       </c>
       <c r="J223" s="4" t="s">
@@ -3354,19 +4011,22 @@
       <c r="K223" s="4" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L223" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="224" ht="12.8">
       <c r="E224" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" ht="12.8">
       <c r="A225" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I227" s="1" t="n">
+    <row r="227" ht="74.6">
+      <c r="I227" s="1">
         <v>69</v>
       </c>
       <c r="J227" s="4" t="s">
@@ -3375,9 +4035,12 @@
       <c r="K227" s="4" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="228" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I228" s="1" t="n">
+      <c r="L227" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="228" ht="116.4">
+      <c r="I228" s="1">
         <v>70</v>
       </c>
       <c r="J228" s="4" t="s">
@@ -3386,9 +4049,12 @@
       <c r="K228" s="4" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="229" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I229" s="1" t="n">
+      <c r="L228" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="229" ht="53.7">
+      <c r="I229" s="1">
         <v>71</v>
       </c>
       <c r="J229" s="4" t="s">
@@ -3397,8 +4063,11 @@
       <c r="K229" s="4" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L229" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="230" ht="12.8">
       <c r="E230" s="1" t="s">
         <v>199</v>
       </c>
@@ -3406,33 +4075,33 @@
         <v>236</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" ht="12.8">
       <c r="E231" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" ht="12.8">
       <c r="A233" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" ht="12.8">
       <c r="J235" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" ht="12.8">
       <c r="E236" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" ht="12.8">
       <c r="A238" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I240" s="1" t="n">
+    <row r="240" ht="74.6">
+      <c r="I240" s="1">
         <v>72</v>
       </c>
       <c r="J240" s="4" t="s">
@@ -3441,8 +4110,11 @@
       <c r="K240" s="4" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L240" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="241" ht="12.8">
       <c r="E241" s="1" t="s">
         <v>65</v>
       </c>
@@ -3450,8 +4122,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I242" s="1" t="n">
+    <row r="242" ht="85.05">
+      <c r="I242" s="1">
         <v>73</v>
       </c>
       <c r="J242" s="4" t="s">
@@ -3460,8 +4132,11 @@
       <c r="K242" s="4" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L242" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="243" ht="12.8">
       <c r="E243" s="1" t="s">
         <v>199</v>
       </c>
@@ -3469,17 +4144,17 @@
         <v>245</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" ht="12.8">
       <c r="E244" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" ht="12.8">
       <c r="A247" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" ht="12.8">
       <c r="E248" s="1" t="s">
         <v>14</v>
       </c>
@@ -3487,8 +4162,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I249" s="1" t="n">
+    <row r="249" ht="43.25">
+      <c r="I249" s="1">
         <v>74</v>
       </c>
       <c r="J249" s="4" t="s">
@@ -3497,8 +4172,11 @@
       <c r="K249" s="4" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L249" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="250" ht="12.8">
       <c r="E250" s="1" t="s">
         <v>250</v>
       </c>
@@ -3506,7 +4184,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" ht="12.8">
       <c r="E251" s="1" t="s">
         <v>252</v>
       </c>
@@ -3514,7 +4192,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" ht="12.8">
       <c r="E252" s="1" t="s">
         <v>253</v>
       </c>
@@ -3522,7 +4200,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" ht="12.8">
       <c r="E253" s="1" t="s">
         <v>254</v>
       </c>
@@ -3530,8 +4208,8 @@
         <v>255</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I254" s="1" t="n">
+    <row r="254" ht="43.25">
+      <c r="I254" s="1">
         <v>75</v>
       </c>
       <c r="J254" s="4" t="s">
@@ -3540,9 +4218,12 @@
       <c r="K254" s="4" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I255" s="1" t="n">
+      <c r="L254" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="255" ht="12.8">
+      <c r="I255" s="1">
         <v>76</v>
       </c>
       <c r="J255" s="1" t="s">
@@ -3551,9 +4232,12 @@
       <c r="K255" s="1" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="256" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I256" s="1" t="n">
+      <c r="L255" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="256" ht="43.25">
+      <c r="I256" s="1">
         <v>77</v>
       </c>
       <c r="J256" s="4" t="s">
@@ -3562,9 +4246,12 @@
       <c r="K256" s="4" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="257" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I257" s="1" t="n">
+      <c r="L256" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="257" ht="85.05">
+      <c r="I257" s="1">
         <v>78</v>
       </c>
       <c r="J257" s="4" t="s">
@@ -3573,9 +4260,12 @@
       <c r="K257" s="4" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="258" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I258" s="1" t="n">
+      <c r="L257" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="258" ht="85.05">
+      <c r="I258" s="1">
         <v>79</v>
       </c>
       <c r="J258" s="4" t="s">
@@ -3584,9 +4274,12 @@
       <c r="K258" s="4" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="259" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I259" s="1" t="n">
+      <c r="L258" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="259" ht="64.15">
+      <c r="I259" s="1">
         <v>80</v>
       </c>
       <c r="J259" s="4" t="s">
@@ -3595,9 +4288,12 @@
       <c r="K259" s="4" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="261" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I261" s="1" t="n">
+      <c r="L259" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="261" ht="95.5">
+      <c r="I261" s="1">
         <v>81</v>
       </c>
       <c r="J261" s="4" t="s">
@@ -3606,13 +4302,16 @@
       <c r="K261" s="4" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L261" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="264" ht="12.8">
       <c r="E264" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" ht="12.8">
       <c r="E265" s="1" t="s">
         <v>65</v>
       </c>
@@ -3620,18 +4319,18 @@
         <v>270</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" ht="12.8">
       <c r="E266" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" ht="12.8">
       <c r="A270" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I272" s="1" t="n">
+    <row r="272" ht="32.8">
+      <c r="I272" s="1">
         <v>82</v>
       </c>
       <c r="J272" s="4" t="s">
@@ -3640,9 +4339,12 @@
       <c r="K272" s="4" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="273" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I273" s="1" t="n">
+      <c r="L272" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="273" ht="85.05">
+      <c r="I273" s="1">
         <v>83</v>
       </c>
       <c r="J273" s="4" t="s">
@@ -3651,9 +4353,12 @@
       <c r="K273" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I274" s="1" t="n">
+      <c r="L273" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="274" ht="12.8">
+      <c r="I274" s="1">
         <v>84</v>
       </c>
       <c r="J274" s="1" t="s">
@@ -3662,8 +4367,11 @@
       <c r="K274" s="7" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L274" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="275" ht="12.8">
       <c r="E275" s="1" t="s">
         <v>199</v>
       </c>
@@ -3671,18 +4379,18 @@
         <v>278</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" ht="12.8">
       <c r="E276" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" ht="12.8">
       <c r="A278" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I280" s="1" t="n">
+    <row r="280" ht="53.7">
+      <c r="I280" s="1">
         <v>85</v>
       </c>
       <c r="J280" s="4" t="s">
@@ -3691,9 +4399,12 @@
       <c r="K280" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="281" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I281" s="1" t="n">
+      <c r="L280" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="281" ht="64.15">
+      <c r="I281" s="1">
         <v>86</v>
       </c>
       <c r="J281" s="4" t="s">
@@ -3702,9 +4413,12 @@
       <c r="K281" s="4" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I282" s="1" t="n">
+      <c r="L281" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="282" ht="12.8">
+      <c r="I282" s="1">
         <v>102</v>
       </c>
       <c r="J282" s="1" t="s">
@@ -3713,19 +4427,22 @@
       <c r="K282" s="1" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L282" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="283" ht="12.8">
       <c r="E283" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" ht="12.8">
       <c r="A285" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I287" s="1" t="n">
+    <row r="287" ht="12.8">
+      <c r="I287" s="1">
         <v>87</v>
       </c>
       <c r="J287" s="1" t="s">
@@ -3734,9 +4451,12 @@
       <c r="K287" s="1" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="288" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I288" s="1" t="n">
+      <c r="L287" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="288" ht="64.15">
+      <c r="I288" s="1">
         <v>88</v>
       </c>
       <c r="J288" s="4" t="s">
@@ -3745,19 +4465,22 @@
       <c r="K288" s="4" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L288" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="289" ht="12.8">
       <c r="E289" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" ht="12.8">
       <c r="A291" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I292" s="1" t="n">
+    <row r="292" ht="12.8">
+      <c r="I292" s="1">
         <v>89</v>
       </c>
       <c r="J292" s="1" t="s">
@@ -3766,9 +4489,12 @@
       <c r="K292" s="1" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="293" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I293" s="1" t="n">
+      <c r="L292" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="293" ht="95.5">
+      <c r="I293" s="1">
         <v>90</v>
       </c>
       <c r="J293" s="4" t="s">
@@ -3777,24 +4503,27 @@
       <c r="K293" s="4" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L293" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="294" ht="12.8">
       <c r="E294" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" ht="12.8">
       <c r="E295" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" ht="12.8">
       <c r="A298" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I299" s="1" t="n">
+    <row r="299" ht="74.6">
+      <c r="I299" s="1">
         <v>91</v>
       </c>
       <c r="J299" s="4" t="s">
@@ -3803,9 +4532,12 @@
       <c r="K299" s="4" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="300" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I300" s="1" t="n">
+      <c r="L299" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="300" ht="74.6">
+      <c r="I300" s="1">
         <v>92</v>
       </c>
       <c r="J300" s="4" t="s">
@@ -3814,8 +4546,11 @@
       <c r="K300" s="4" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L300" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="301" ht="12.8">
       <c r="E301" s="1" t="s">
         <v>65</v>
       </c>
@@ -3823,7 +4558,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" ht="12.8">
       <c r="E302" s="1" t="s">
         <v>199</v>
       </c>
@@ -3831,18 +4566,18 @@
         <v>302</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" ht="12.8">
       <c r="E303" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" ht="12.8">
       <c r="A305" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I306" s="1" t="n">
+    <row r="306" ht="64.15">
+      <c r="I306" s="1">
         <v>93</v>
       </c>
       <c r="J306" s="4" t="s">
@@ -3851,9 +4586,12 @@
       <c r="K306" s="4" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="307" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I307" s="1" t="n">
+      <c r="L306" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="307" ht="116.4">
+      <c r="I307" s="1">
         <v>94</v>
       </c>
       <c r="J307" s="4" t="s">
@@ -3862,8 +4600,11 @@
       <c r="K307" s="4" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L307" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="308" ht="12.8">
       <c r="E308" s="1" t="s">
         <v>65</v>
       </c>
@@ -3871,18 +4612,18 @@
         <v>308</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" ht="12.8">
       <c r="E309" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" ht="12.8">
       <c r="A311" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I312" s="1" t="n">
+    <row r="312" ht="85.05">
+      <c r="I312" s="1">
         <v>95</v>
       </c>
       <c r="J312" s="4" t="s">
@@ -3891,9 +4632,12 @@
       <c r="K312" s="4" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="313" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I313" s="1" t="n">
+      <c r="L312" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="313" ht="95.5">
+      <c r="I313" s="1">
         <v>96</v>
       </c>
       <c r="J313" s="4" t="s">
@@ -3902,24 +4646,27 @@
       <c r="K313" s="4" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L313" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="314" ht="12.8">
       <c r="E314" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" ht="12.8">
       <c r="A316" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" ht="12.8">
       <c r="E317" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I318" s="1" t="n">
+    <row r="318" ht="74.6">
+      <c r="I318" s="1">
         <v>97</v>
       </c>
       <c r="J318" s="4" t="s">
@@ -3928,19 +4675,22 @@
       <c r="K318" s="4" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L318" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="320" ht="12.8">
       <c r="E320" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" ht="12.8">
       <c r="A323" s="1" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I324" s="1" t="n">
+    <row r="324" ht="64.15">
+      <c r="I324" s="1">
         <v>98</v>
       </c>
       <c r="J324" s="4" t="s">
@@ -3949,9 +4699,12 @@
       <c r="K324" s="4" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="325" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I325" s="1" t="n">
+      <c r="L324" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="325" ht="105.95">
+      <c r="I325" s="1">
         <v>99</v>
       </c>
       <c r="J325" s="4" t="s">
@@ -3960,9 +4713,12 @@
       <c r="K325" s="4" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="326" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I326" s="1" t="n">
+      <c r="L325" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="326" ht="74.6">
+      <c r="I326" s="1">
         <v>100</v>
       </c>
       <c r="J326" s="4" t="s">
@@ -3971,8 +4727,11 @@
       <c r="K326" s="4" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L326" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="328" ht="12.8">
       <c r="E328" s="1" t="s">
         <v>65</v>
       </c>
@@ -3980,7 +4739,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" ht="12.8">
       <c r="E329" s="1" t="s">
         <v>199</v>
       </c>
@@ -3988,23 +4747,23 @@
         <v>325</v>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" ht="12.8">
       <c r="E330" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" ht="12.8">
       <c r="A332" s="1" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" ht="12.8">
       <c r="E334" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I335" s="1" t="n">
+    <row r="335" ht="74.6">
+      <c r="I335" s="1">
         <v>101</v>
       </c>
       <c r="J335" s="4" t="s">
@@ -4013,18 +4772,21 @@
       <c r="K335" s="4" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L335" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="336" ht="12.8">
       <c r="E336" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" ht="12.8">
       <c r="A338" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" ht="12.8">
       <c r="E339" s="1" t="s">
         <v>14</v>
       </c>
@@ -4032,11 +4794,11 @@
         <v>330</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" ht="12.8">
       <c r="F341" s="8"/>
     </row>
-    <row r="342" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I342" s="1" t="n">
+    <row r="342" ht="64.15">
+      <c r="I342" s="1">
         <v>103</v>
       </c>
       <c r="J342" s="5" t="s">
@@ -4045,9 +4807,12 @@
       <c r="K342" s="4" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="343" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I343" s="1" t="n">
+      <c r="L342" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="343" ht="46.25">
+      <c r="I343" s="1">
         <v>120</v>
       </c>
       <c r="J343" s="5" t="s">
@@ -4056,15 +4821,18 @@
       <c r="K343" s="4" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L343" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="344" ht="13.8">
       <c r="B344" s="1" t="s">
         <v>335</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I344" s="1" t="n">
+      <c r="I344" s="1">
         <v>121</v>
       </c>
       <c r="J344" s="5" t="s">
@@ -4073,15 +4841,18 @@
       <c r="K344" s="4" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L344" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="345" ht="13.8">
       <c r="B345" s="1" t="s">
         <v>338</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I345" s="1" t="n">
+      <c r="I345" s="1">
         <v>122</v>
       </c>
       <c r="J345" s="5" t="s">
@@ -4090,19 +4861,22 @@
       <c r="K345" s="4" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L345" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="346" ht="13.8">
       <c r="J346" s="5"/>
       <c r="K346" s="4"/>
     </row>
-    <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" ht="13.8">
       <c r="A347" s="1" t="s">
         <v>335</v>
       </c>
       <c r="J347" s="5"/>
       <c r="K347" s="4"/>
     </row>
-    <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" ht="13.8">
       <c r="E348" s="1" t="s">
         <v>199</v>
       </c>
@@ -4112,8 +4886,8 @@
       <c r="J348" s="5"/>
       <c r="K348" s="4"/>
     </row>
-    <row r="349" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I349" s="1" t="n">
+    <row r="349" ht="64.15">
+      <c r="I349" s="1">
         <v>125</v>
       </c>
       <c r="J349" s="5" t="s">
@@ -4122,12 +4896,15 @@
       <c r="K349" s="4" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L349" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="350" ht="13.8">
       <c r="G350" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I350" s="1" t="n">
+      <c r="I350" s="1">
         <v>108</v>
       </c>
       <c r="J350" s="5" t="s">
@@ -4136,12 +4913,15 @@
       <c r="K350" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L350" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="351" ht="13.8">
       <c r="G351" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I351" s="1" t="n">
+      <c r="I351" s="1">
         <v>109</v>
       </c>
       <c r="J351" s="5" t="s">
@@ -4150,12 +4930,15 @@
       <c r="K351" s="1" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="352" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L351" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="352" ht="53.7">
       <c r="G352" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I352" s="1" t="n">
+      <c r="I352" s="1">
         <v>110</v>
       </c>
       <c r="J352" s="5" t="s">
@@ -4164,12 +4947,15 @@
       <c r="K352" s="4" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L352" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="353" ht="13.8">
       <c r="G353" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I353" s="1" t="n">
+      <c r="I353" s="1">
         <v>104</v>
       </c>
       <c r="J353" s="3" t="s">
@@ -4178,9 +4964,12 @@
       <c r="K353" s="1" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="354" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I354" s="1" t="n">
+      <c r="L353" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="354" ht="64.15">
+      <c r="I354" s="1">
         <v>105</v>
       </c>
       <c r="J354" s="5" t="s">
@@ -4189,12 +4978,15 @@
       <c r="K354" s="4" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L354" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="355" ht="12.8">
       <c r="G355" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I355" s="1" t="n">
+      <c r="I355" s="1">
         <v>111</v>
       </c>
       <c r="J355" s="1" t="s">
@@ -4203,12 +4995,15 @@
       <c r="K355" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L355" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="356" ht="12.8">
       <c r="G356" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="I356" s="1" t="n">
+      <c r="I356" s="1">
         <v>119</v>
       </c>
       <c r="J356" s="1" t="s">
@@ -4217,9 +5012,12 @@
       <c r="K356" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I357" s="1" t="n">
+      <c r="L356" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="357" ht="12.8">
+      <c r="I357" s="1">
         <v>107</v>
       </c>
       <c r="J357" s="1" t="s">
@@ -4228,12 +5026,15 @@
       <c r="K357" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L357" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="358" ht="13.8">
       <c r="G358" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I358" s="1" t="n">
+      <c r="I358" s="1">
         <v>112</v>
       </c>
       <c r="J358" s="3" t="s">
@@ -4242,9 +5043,12 @@
       <c r="K358" s="1" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I359" s="1" t="n">
+      <c r="L358" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="359" ht="13.8">
+      <c r="I359" s="1">
         <v>113</v>
       </c>
       <c r="J359" s="10" t="s">
@@ -4253,12 +5057,15 @@
       <c r="K359" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="360" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L359" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="360" ht="74.6">
       <c r="G360" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I360" s="1" t="n">
+      <c r="I360" s="1">
         <v>114</v>
       </c>
       <c r="J360" s="5" t="s">
@@ -4267,12 +5074,15 @@
       <c r="K360" s="4" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="361" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L360" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="361" ht="105.95">
       <c r="G361" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I361" s="1" t="n">
+      <c r="I361" s="1">
         <v>115</v>
       </c>
       <c r="J361" s="5" t="s">
@@ -4281,9 +5091,12 @@
       <c r="K361" s="4" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="362" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I362" s="1" t="n">
+      <c r="L361" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="362" ht="61.15">
+      <c r="I362" s="1">
         <v>116</v>
       </c>
       <c r="J362" s="11" t="s">
@@ -4292,24 +5105,27 @@
       <c r="K362" s="4" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L362" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="363" ht="12.8">
       <c r="E363" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" ht="12.8">
       <c r="E365" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" ht="12.8">
       <c r="A369" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I371" s="1" t="n">
+    <row r="371" ht="12.8">
+      <c r="I371" s="1">
         <v>123</v>
       </c>
       <c r="J371" s="1" t="s">
@@ -4318,20 +5134,23 @@
       <c r="K371" s="1" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L371" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="373" ht="12.8">
       <c r="E373" s="1" t="s">
         <v>195</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
